--- a/data/google-spreadsheet/M3GIM-Objekte.xlsx
+++ b/data/google-spreadsheet/M3GIM-Objekte.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7081" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7099" uniqueCount="1389">
   <si>
     <t>archivsignatur</t>
   </si>
@@ -658,6 +658,9 @@
     <t>Tätigkeitsliste 1939 bis 1949</t>
   </si>
   <si>
+    <t>erledigt</t>
+  </si>
+  <si>
     <t>Tätigkeitsliste 1949 bis 1952</t>
   </si>
   <si>
@@ -944,9 +947,6 @@
   </si>
   <si>
     <t>Begleitbrief zu Originalvertrag Genf von Direktor Gruder-Guntram an Ira Malaniuk vom 16.08.1956</t>
-  </si>
-  <si>
-    <t>erledigt</t>
   </si>
   <si>
     <t>Brief Wieland Wagner an Ira Malaniuk vom 22.03.1955</t>
@@ -7899,8 +7899,12 @@
       <c r="K91" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M91" s="6"/>
-      <c r="N91" s="6"/>
+      <c r="M91" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N91" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O91" s="6"/>
       <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
@@ -7917,7 +7921,7 @@
         <v>16.0</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E92" s="21" t="s">
         <v>199</v>
@@ -7940,8 +7944,12 @@
       <c r="K92" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M92" s="6"/>
-      <c r="N92" s="6"/>
+      <c r="M92" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N92" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O92" s="6"/>
       <c r="P92" s="6"/>
       <c r="Q92" s="6"/>
@@ -7958,7 +7966,7 @@
         <v>17.0</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E93" s="21" t="s">
         <v>199</v>
@@ -7981,8 +7989,12 @@
       <c r="K93" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M93" s="6"/>
-      <c r="N93" s="6"/>
+      <c r="M93" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N93" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O93" s="6"/>
       <c r="P93" s="6"/>
       <c r="Q93" s="6"/>
@@ -7999,7 +8011,7 @@
         <v>18.0</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E94" s="21" t="s">
         <v>199</v>
@@ -8022,8 +8034,12 @@
       <c r="K94" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M94" s="6"/>
-      <c r="N94" s="6"/>
+      <c r="M94" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N94" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O94" s="6"/>
       <c r="P94" s="6"/>
       <c r="Q94" s="6"/>
@@ -8040,7 +8056,7 @@
         <v>19.0</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E95" s="21" t="s">
         <v>199</v>
@@ -8063,8 +8079,12 @@
       <c r="K95" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M95" s="6"/>
-      <c r="N95" s="6"/>
+      <c r="M95" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N95" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
@@ -8081,7 +8101,7 @@
         <v>20.0</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E96" s="21" t="s">
         <v>199</v>
@@ -8104,8 +8124,12 @@
       <c r="K96" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M96" s="6"/>
-      <c r="N96" s="6"/>
+      <c r="M96" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N96" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O96" s="6"/>
       <c r="P96" s="6"/>
       <c r="Q96" s="6"/>
@@ -8122,7 +8146,7 @@
         <v>21.0</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E97" s="21" t="s">
         <v>199</v>
@@ -8145,8 +8169,12 @@
       <c r="K97" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M97" s="6"/>
-      <c r="N97" s="6"/>
+      <c r="M97" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N97" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O97" s="6"/>
       <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
@@ -8163,7 +8191,7 @@
         <v>22.0</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E98" s="21" t="s">
         <v>199</v>
@@ -8186,8 +8214,12 @@
       <c r="K98" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M98" s="6"/>
-      <c r="N98" s="6"/>
+      <c r="M98" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N98" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O98" s="6"/>
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
@@ -8204,7 +8236,7 @@
         <v>23.0</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E99" s="21" t="s">
         <v>199</v>
@@ -8227,8 +8259,12 @@
       <c r="K99" s="9">
         <v>46168.0</v>
       </c>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
+      <c r="M99" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="N99" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="O99" s="6"/>
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
@@ -8245,7 +8281,7 @@
         <v>24.0</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E100" s="21" t="s">
         <v>199</v>
@@ -8286,7 +8322,7 @@
         <v>25.0</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E101" s="21" t="s">
         <v>199</v>
@@ -8327,7 +8363,7 @@
         <v>26.0</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E102" s="21" t="s">
         <v>199</v>
@@ -8368,7 +8404,7 @@
         <v>27.0</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E103" s="21" t="s">
         <v>199</v>
@@ -8409,7 +8445,7 @@
         <v>28.0</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E104" s="21" t="s">
         <v>199</v>
@@ -8450,7 +8486,7 @@
         <v>29.0</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E105" s="21" t="s">
         <v>199</v>
@@ -8485,14 +8521,14 @@
         <v>1.0</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C106" s="23"/>
       <c r="D106" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F106" s="10"/>
       <c r="G106" s="10" t="s">
@@ -8524,13 +8560,13 @@
         <v>1.0</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C107" s="3">
         <v>1.0</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="5" t="s">
@@ -8543,13 +8579,13 @@
         <v>178</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K107" s="9">
         <v>46108.0</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
@@ -8563,13 +8599,13 @@
         <v>1.0</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C108" s="3">
         <v>2.0</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E108" s="9">
         <v>30951.0</v>
@@ -8584,7 +8620,7 @@
         <v>113</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K108" s="9">
         <v>46108.0</v>
@@ -8601,19 +8637,19 @@
         <v>1.0</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C109" s="3">
         <v>3.0</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E109" s="21">
         <v>1976.0</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>193</v>
@@ -8622,7 +8658,7 @@
         <v>113</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K109" s="9">
         <v>46108.0</v>
@@ -8639,19 +8675,19 @@
         <v>1.0</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C110" s="3">
         <v>4.0</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E110" s="9">
         <v>31061.0</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>193</v>
@@ -8660,7 +8696,7 @@
         <v>113</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K110" s="9">
         <v>46108.0</v>
@@ -8677,16 +8713,16 @@
         <v>1.0</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C111" s="3">
         <v>5.0</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E111" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>122</v>
@@ -8698,7 +8734,7 @@
         <v>113</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K111" s="9">
         <v>46108.0</v>
@@ -8718,13 +8754,13 @@
         <v>1.0</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C112" s="3">
         <v>6.0</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E112" s="9">
         <v>31022.0</v>
@@ -8759,13 +8795,13 @@
         <v>1.0</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C113" s="3">
         <v>7.0</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E113" s="9">
         <v>31461.0</v>
@@ -8797,13 +8833,13 @@
         <v>1.0</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C114" s="3">
         <v>8.0</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E114" s="9">
         <v>31015.0</v>
@@ -8838,13 +8874,13 @@
         <v>1.0</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C115" s="3">
         <v>9.0</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E115" s="9">
         <v>28720.0</v>
@@ -8876,16 +8912,16 @@
         <v>1.0</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C116" s="11" t="s">
         <v>119</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F116" s="10"/>
       <c r="G116" s="10" t="s">
@@ -8894,10 +8930,10 @@
       <c r="H116" s="10"/>
       <c r="I116" s="10"/>
       <c r="J116" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L116" s="10"/>
       <c r="M116" s="6"/>
@@ -8919,13 +8955,13 @@
         <v>1.0</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C117" s="3">
         <v>1.0</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E117" s="9">
         <v>19071.0</v>
@@ -8943,13 +8979,13 @@
         <v>141</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K117" s="9">
         <v>46045.0</v>
       </c>
       <c r="L117" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
@@ -8963,13 +8999,13 @@
         <v>1.0</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C118" s="3">
         <v>2.0</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E118" s="9">
         <v>19141.0</v>
@@ -8984,13 +9020,13 @@
         <v>113</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K118" s="9">
         <v>46045.0</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
@@ -9004,13 +9040,13 @@
         <v>1.0</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C119" s="3">
         <v>3.0</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E119" s="9">
         <v>19546.0</v>
@@ -9019,7 +9055,7 @@
         <v>122</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>113</v>
@@ -9031,7 +9067,7 @@
         <v>46045.0</v>
       </c>
       <c r="L119" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
@@ -9045,13 +9081,13 @@
         <v>1.0</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C120" s="3">
         <v>4.0</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E120" s="9">
         <v>19631.0</v>
@@ -9089,13 +9125,13 @@
         <v>1.0</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C121" s="3">
         <v>5.0</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E121" s="8"/>
       <c r="F121" s="5" t="s">
@@ -9108,7 +9144,7 @@
         <v>113</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J121" s="8"/>
       <c r="K121" s="9">
@@ -9129,13 +9165,13 @@
         <v>1.0</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E122" s="21">
         <v>1957.0</v>
@@ -9171,13 +9207,13 @@
         <v>1.0</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E123" s="9">
         <v>20941.0</v>
@@ -9186,7 +9222,7 @@
         <v>122</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H123" s="5" t="s">
         <v>113</v>
@@ -9213,13 +9249,13 @@
         <v>1.0</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E124" s="9">
         <v>20995.0</v>
@@ -9228,7 +9264,7 @@
         <v>122</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H124" s="5" t="s">
         <v>113</v>
@@ -9255,13 +9291,13 @@
         <v>1.0</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E125" s="9">
         <v>21001.0</v>
@@ -9270,7 +9306,7 @@
         <v>122</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H125" s="5" t="s">
         <v>113</v>
@@ -9297,13 +9333,13 @@
         <v>1.0</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E126" s="9">
         <v>21124.0</v>
@@ -9312,7 +9348,7 @@
         <v>122</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H126" s="5" t="s">
         <v>113</v>
@@ -9339,13 +9375,13 @@
         <v>1.0</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E127" s="9">
         <v>21159.0</v>
@@ -9354,7 +9390,7 @@
         <v>122</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>113</v>
@@ -9380,13 +9416,13 @@
         <v>1.0</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E128" s="9">
         <v>21257.0</v>
@@ -9395,7 +9431,7 @@
         <v>122</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H128" s="5" t="s">
         <v>113</v>
@@ -9421,13 +9457,13 @@
         <v>1.0</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E129" s="9">
         <v>20955.0</v>
@@ -9436,7 +9472,7 @@
         <v>122</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H129" s="5" t="s">
         <v>113</v>
@@ -9462,13 +9498,13 @@
         <v>1.0</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C130" s="3">
         <v>6.0</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E130" s="9">
         <v>21679.0</v>
@@ -9477,7 +9513,7 @@
         <v>122</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H130" s="5" t="s">
         <v>113</v>
@@ -9503,13 +9539,13 @@
         <v>1.0</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C131" s="3">
         <v>7.0</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E131" s="9">
         <v>22606.0</v>
@@ -9544,13 +9580,13 @@
         <v>1.0</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C132" s="3">
         <v>8.0</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E132" s="9">
         <v>23251.0</v>
@@ -9562,10 +9598,10 @@
         <v>123</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="9">
@@ -9583,13 +9619,13 @@
         <v>1.0</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C133" s="3">
         <v>9.0</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E133" s="9">
         <v>23078.0</v>
@@ -9627,13 +9663,13 @@
         <v>1.0</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C134" s="3">
         <v>10.0</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E134" s="9">
         <v>23607.0</v>
@@ -9671,13 +9707,13 @@
         <v>1.0</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C135" s="3">
         <v>11.0</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E135" s="9">
         <v>25160.0</v>
@@ -9715,13 +9751,13 @@
         <v>1.0</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C136" s="3">
         <v>12.0</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E136" s="9">
         <v>25106.0</v>
@@ -9759,13 +9795,13 @@
         <v>1.0</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C137" s="3">
         <v>13.0</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E137" s="8"/>
       <c r="F137" s="5" t="s">
@@ -9796,13 +9832,13 @@
         <v>1.0</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C138" s="3">
         <v>14.0</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E138" s="9">
         <v>25106.0</v>
@@ -9837,13 +9873,13 @@
         <v>1.0</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C139" s="3">
         <v>15.0</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E139" s="8"/>
       <c r="F139" s="5" t="s">
@@ -9876,13 +9912,13 @@
         <v>1.0</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C140" s="3">
         <v>16.0</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E140" s="8"/>
       <c r="F140" s="5" t="s">
@@ -9915,13 +9951,13 @@
         <v>1.0</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C141" s="3">
         <v>17.0</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E141" s="9">
         <v>25106.0</v>
@@ -9956,13 +9992,13 @@
         <v>1.0</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C142" s="3">
         <v>18.0</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E142" s="8"/>
       <c r="F142" s="5" t="s">
@@ -9995,20 +10031,20 @@
         <v>1.0</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C143" s="3">
         <v>19.0</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E143" s="8"/>
       <c r="F143" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H143" s="5" t="s">
         <v>113</v>
@@ -10034,13 +10070,13 @@
         <v>1.0</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C144" s="3">
         <v>20.0</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E144" s="8"/>
       <c r="F144" s="5" t="s">
@@ -10053,7 +10089,7 @@
         <v>113</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K144" s="9">
         <v>46064.0</v>
@@ -10073,13 +10109,13 @@
         <v>1.0</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C145" s="3">
         <v>21.0</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E145" s="8"/>
       <c r="F145" s="5" t="s">
@@ -10092,7 +10128,7 @@
         <v>113</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K145" s="9">
         <v>46064.0</v>
@@ -10109,14 +10145,14 @@
         <v>1.0</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C146" s="24"/>
       <c r="D146" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E146" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F146" s="17"/>
       <c r="G146" s="17" t="s">
@@ -10125,10 +10161,10 @@
       <c r="H146" s="17"/>
       <c r="I146" s="17"/>
       <c r="J146" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K146" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L146" s="17"/>
       <c r="M146" s="6"/>
@@ -10150,7 +10186,7 @@
         <v>1.0</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C147" s="3">
         <v>1.0</v>
@@ -10172,7 +10208,7 @@
         <v>1.0</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C148" s="3">
         <v>2.0</v>
@@ -10194,7 +10230,7 @@
         <v>1.0</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C149" s="3">
         <v>3.0</v>
@@ -10216,7 +10252,7 @@
         <v>1.0</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C150" s="3">
         <v>4.0</v>
@@ -10238,7 +10274,7 @@
         <v>1.0</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C151" s="3">
         <v>5.0</v>
@@ -10260,7 +10296,7 @@
         <v>1.0</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C152" s="3">
         <v>6.0</v>
@@ -10282,7 +10318,7 @@
         <v>1.0</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C153" s="3">
         <v>7.0</v>
@@ -10304,7 +10340,7 @@
         <v>1.0</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C154" s="3">
         <v>8.0</v>
@@ -10326,7 +10362,7 @@
         <v>1.0</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C155" s="3">
         <v>9.0</v>
@@ -10348,7 +10384,7 @@
         <v>1.0</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C156" s="3">
         <v>10.0</v>
@@ -10370,7 +10406,7 @@
         <v>1.0</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C157" s="3">
         <v>11.0</v>
@@ -10392,7 +10428,7 @@
         <v>1.0</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C158" s="3">
         <v>12.0</v>
@@ -10414,7 +10450,7 @@
         <v>1.0</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C159" s="3">
         <v>13.0</v>
@@ -10436,7 +10472,7 @@
         <v>1.0</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C160" s="3">
         <v>14.0</v>
@@ -10458,7 +10494,7 @@
         <v>1.0</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C161" s="3">
         <v>15.0</v>
@@ -10480,7 +10516,7 @@
         <v>1.0</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C162" s="3">
         <v>16.0</v>
@@ -10502,7 +10538,7 @@
         <v>1.0</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C163" s="3">
         <v>17.0</v>
@@ -10524,7 +10560,7 @@
         <v>1.0</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C164" s="3">
         <v>18.0</v>
@@ -10546,7 +10582,7 @@
         <v>1.0</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C165" s="3">
         <v>19.0</v>
@@ -10568,7 +10604,7 @@
         <v>1.0</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C166" s="3">
         <v>20.0</v>
@@ -10590,7 +10626,7 @@
         <v>1.0</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C167" s="3">
         <v>21.0</v>
@@ -10612,7 +10648,7 @@
         <v>1.0</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C168" s="3">
         <v>22.0</v>
@@ -10634,7 +10670,7 @@
         <v>1.0</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C169" s="3">
         <v>23.0</v>
@@ -10656,7 +10692,7 @@
         <v>1.0</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C170" s="3">
         <v>24.0</v>
@@ -10678,7 +10714,7 @@
         <v>1.0</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C171" s="3">
         <v>25.0</v>
@@ -10700,7 +10736,7 @@
         <v>1.0</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C172" s="3">
         <v>26.0</v>
@@ -10722,7 +10758,7 @@
         <v>1.0</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C173" s="3">
         <v>27.0</v>
@@ -10744,7 +10780,7 @@
         <v>1.0</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C174" s="3">
         <v>28.0</v>
@@ -10766,7 +10802,7 @@
         <v>1.0</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C175" s="3">
         <v>29.0</v>
@@ -10788,7 +10824,7 @@
         <v>1.0</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C176" s="3">
         <v>30.0</v>
@@ -10810,7 +10846,7 @@
         <v>1.0</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C177" s="3">
         <v>31.0</v>
@@ -10832,7 +10868,7 @@
         <v>1.0</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C178" s="3">
         <v>32.0</v>
@@ -10854,7 +10890,7 @@
         <v>1.0</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C179" s="3">
         <v>33.0</v>
@@ -10876,7 +10912,7 @@
         <v>1.0</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C180" s="3">
         <v>34.0</v>
@@ -10898,7 +10934,7 @@
         <v>1.0</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C181" s="3">
         <v>35.0</v>
@@ -10920,7 +10956,7 @@
         <v>1.0</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C182" s="3">
         <v>36.0</v>
@@ -10942,7 +10978,7 @@
         <v>1.0</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C183" s="3">
         <v>37.0</v>
@@ -10964,7 +11000,7 @@
         <v>1.0</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C184" s="3">
         <v>38.0</v>
@@ -10986,7 +11022,7 @@
         <v>1.0</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C185" s="3">
         <v>39.0</v>
@@ -11008,7 +11044,7 @@
         <v>1.0</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C186" s="3">
         <v>40.0</v>
@@ -11030,25 +11066,25 @@
         <v>1.0</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E187" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F187" s="6"/>
       <c r="G187" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H187" s="6"/>
       <c r="J187" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K187" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M187" s="6"/>
       <c r="N187" s="6"/>
@@ -11062,25 +11098,25 @@
         <v>1.0</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E188" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F188" s="6"/>
       <c r="G188" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H188" s="6"/>
       <c r="J188" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K188" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M188" s="6"/>
       <c r="N188" s="6"/>
@@ -11094,14 +11130,14 @@
         <v>1.0</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C189" s="24"/>
       <c r="D189" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E189" s="19" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F189" s="17"/>
       <c r="G189" s="17" t="s">
@@ -11110,10 +11146,10 @@
       <c r="H189" s="17"/>
       <c r="I189" s="17"/>
       <c r="J189" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K189" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L189" s="17"/>
       <c r="M189" s="6"/>
@@ -11135,13 +11171,13 @@
         <v>1.0</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C190" s="3">
         <v>1.0</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E190" s="9">
         <v>20683.0</v>
@@ -11165,25 +11201,25 @@
         <v>46189.0</v>
       </c>
       <c r="L190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R190" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -11191,7 +11227,7 @@
         <v>1.0</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C191" s="3">
         <v>2.0</v>
@@ -11221,25 +11257,25 @@
         <v>46189.0</v>
       </c>
       <c r="L191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R191" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
@@ -11247,7 +11283,7 @@
         <v>1.0</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C192" s="3">
         <v>3.0</v>
@@ -11277,25 +11313,25 @@
         <v>46189.0</v>
       </c>
       <c r="L192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R192" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -11303,7 +11339,7 @@
         <v>1.0</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C193" s="3">
         <v>4.0</v>
@@ -11333,25 +11369,25 @@
         <v>46189.0</v>
       </c>
       <c r="L193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R193" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
@@ -11359,7 +11395,7 @@
         <v>1.0</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C194" s="3">
         <v>5.0</v>
@@ -11389,25 +11425,25 @@
         <v>46189.0</v>
       </c>
       <c r="L194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R194" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
@@ -11415,7 +11451,7 @@
         <v>1.0</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C195" s="3">
         <v>6.0</v>
@@ -11445,25 +11481,25 @@
         <v>46189.0</v>
       </c>
       <c r="L195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R195" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
@@ -11471,7 +11507,7 @@
         <v>1.0</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C196" s="3">
         <v>7.0</v>
@@ -11501,25 +11537,25 @@
         <v>46189.0</v>
       </c>
       <c r="L196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R196" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
@@ -11527,7 +11563,7 @@
         <v>1.0</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C197" s="3">
         <v>8.0</v>
@@ -11557,25 +11593,25 @@
         <v>46189.0</v>
       </c>
       <c r="L197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R197" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
@@ -11583,7 +11619,7 @@
         <v>1.0</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C198" s="3">
         <v>9.0</v>
@@ -11613,25 +11649,25 @@
         <v>46189.0</v>
       </c>
       <c r="L198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R198" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
@@ -11639,7 +11675,7 @@
         <v>1.0</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C199" s="3">
         <v>10.0</v>
@@ -11669,25 +11705,25 @@
         <v>46189.0</v>
       </c>
       <c r="L199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R199" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
@@ -11695,7 +11731,7 @@
         <v>1.0</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C200" s="3">
         <v>11.0</v>
@@ -11725,7 +11761,7 @@
         <v>46116.0</v>
       </c>
       <c r="L200" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M200" s="6"/>
       <c r="N200" s="6"/>
@@ -11739,7 +11775,7 @@
         <v>1.0</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C201" s="3">
         <v>12.0</v>
@@ -11767,7 +11803,7 @@
         <v>46116.0</v>
       </c>
       <c r="L201" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M201" s="6"/>
       <c r="N201" s="6"/>
@@ -11781,7 +11817,7 @@
         <v>1.0</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C202" s="3">
         <v>13.0</v>
@@ -11811,7 +11847,7 @@
         <v>46118.0</v>
       </c>
       <c r="L202" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M202" s="6"/>
       <c r="N202" s="6"/>
@@ -11825,7 +11861,7 @@
         <v>1.0</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C203" s="3">
         <v>14.0</v>
@@ -11855,7 +11891,7 @@
         <v>46118.0</v>
       </c>
       <c r="L203" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M203" s="6"/>
       <c r="N203" s="6"/>
@@ -11869,7 +11905,7 @@
         <v>1.0</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C204" s="3">
         <v>15.0</v>
@@ -11899,7 +11935,7 @@
         <v>46118.0</v>
       </c>
       <c r="L204" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M204" s="6"/>
       <c r="N204" s="6"/>
@@ -11913,7 +11949,7 @@
         <v>1.0</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C205" s="3">
         <v>16.0</v>
@@ -11934,7 +11970,7 @@
         <v>113</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J205" s="5" t="s">
         <v>170</v>
@@ -11943,7 +11979,7 @@
         <v>46127.0</v>
       </c>
       <c r="L205" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M205" s="6"/>
       <c r="N205" s="6"/>
@@ -11957,7 +11993,7 @@
         <v>1.0</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C206" s="3">
         <v>17.0</v>
@@ -11985,7 +12021,7 @@
         <v>46127.0</v>
       </c>
       <c r="L206" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M206" s="6"/>
       <c r="N206" s="6"/>
@@ -11999,7 +12035,7 @@
         <v>1.0</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C207" s="3">
         <v>18.0</v>
@@ -12029,7 +12065,7 @@
         <v>46130.0</v>
       </c>
       <c r="L207" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M207" s="6"/>
       <c r="N207" s="6"/>
@@ -12043,7 +12079,7 @@
         <v>1.0</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C208" s="3">
         <v>19.0</v>
@@ -12073,7 +12109,7 @@
         <v>46131.0</v>
       </c>
       <c r="L208" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M208" s="6"/>
       <c r="N208" s="6"/>
@@ -12087,7 +12123,7 @@
         <v>1.0</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C209" s="3">
         <v>20.0</v>
@@ -12117,7 +12153,7 @@
         <v>46131.0</v>
       </c>
       <c r="L209" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M209" s="6"/>
       <c r="N209" s="6"/>
@@ -12131,7 +12167,7 @@
         <v>1.0</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C210" s="3">
         <v>21.0</v>
@@ -12161,25 +12197,25 @@
         <v>46189.0</v>
       </c>
       <c r="L210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R210" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="211" ht="15.75" customHeight="1">
@@ -12198,11 +12234,11 @@
       </c>
       <c r="F211" s="6"/>
       <c r="G211" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H211" s="6"/>
       <c r="J211" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K211" s="8" t="s">
         <v>336</v>
@@ -12234,7 +12270,7 @@
       </c>
       <c r="H212" s="6"/>
       <c r="J212" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K212" s="8" t="s">
         <v>336</v>
@@ -12266,7 +12302,7 @@
       </c>
       <c r="H213" s="6"/>
       <c r="J213" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K213" s="8" t="s">
         <v>336</v>
@@ -12298,7 +12334,7 @@
       </c>
       <c r="H214" s="6"/>
       <c r="J214" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K214" s="8" t="s">
         <v>336</v>
@@ -12330,7 +12366,7 @@
       </c>
       <c r="H215" s="6"/>
       <c r="J215" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K215" s="8" t="s">
         <v>336</v>
@@ -12377,25 +12413,25 @@
         <v>46227.0</v>
       </c>
       <c r="L216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R216" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" ht="15.75" customHeight="1">
@@ -12433,25 +12469,25 @@
         <v>46227.0</v>
       </c>
       <c r="L217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R217" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" ht="15.75" customHeight="1">
@@ -12489,25 +12525,25 @@
         <v>46227.0</v>
       </c>
       <c r="L218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R218" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -12545,25 +12581,25 @@
         <v>46227.0</v>
       </c>
       <c r="L219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R219" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -12601,25 +12637,25 @@
         <v>46227.0</v>
       </c>
       <c r="L220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R220" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="221" ht="15.75" customHeight="1">
@@ -12657,25 +12693,25 @@
         <v>46245.0</v>
       </c>
       <c r="L221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R221" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
@@ -12713,25 +12749,25 @@
         <v>46245.0</v>
       </c>
       <c r="L222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R222" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="223" ht="15.75" customHeight="1">
@@ -12769,25 +12805,25 @@
         <v>46245.0</v>
       </c>
       <c r="L223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R223" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -12825,25 +12861,25 @@
         <v>46245.0</v>
       </c>
       <c r="L224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R224" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="225" ht="15.75" customHeight="1">
@@ -12881,25 +12917,25 @@
         <v>46245.0</v>
       </c>
       <c r="L225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R225" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
@@ -12937,25 +12973,25 @@
         <v>46245.0</v>
       </c>
       <c r="L226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R226" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -12993,25 +13029,25 @@
         <v>46245.0</v>
       </c>
       <c r="L227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R227" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
@@ -13049,25 +13085,25 @@
         <v>46248.0</v>
       </c>
       <c r="L228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R228" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -13105,25 +13141,25 @@
         <v>46251.0</v>
       </c>
       <c r="L229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R229" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
@@ -13161,25 +13197,25 @@
         <v>46251.0</v>
       </c>
       <c r="L230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R230" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="231" ht="15.75" customHeight="1">
@@ -13217,25 +13253,25 @@
         <v>46251.0</v>
       </c>
       <c r="L231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R231" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -13273,25 +13309,25 @@
         <v>46251.0</v>
       </c>
       <c r="L232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R232" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="233" ht="15.75" customHeight="1">
@@ -13329,25 +13365,25 @@
         <v>46251.0</v>
       </c>
       <c r="L233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R233" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="234" ht="15.75" customHeight="1">
@@ -13385,25 +13421,25 @@
         <v>46251.0</v>
       </c>
       <c r="L234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R234" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="235" ht="15.75" customHeight="1">
@@ -13462,11 +13498,11 @@
       </c>
       <c r="F237" s="6"/>
       <c r="G237" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H237" s="6"/>
       <c r="J237" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K237" s="8" t="s">
         <v>336</v>
@@ -13498,7 +13534,7 @@
       </c>
       <c r="H238" s="6"/>
       <c r="J238" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K238" s="8" t="s">
         <v>336</v>
@@ -13530,7 +13566,7 @@
       </c>
       <c r="H239" s="6"/>
       <c r="J239" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K239" s="8" t="s">
         <v>336</v>
@@ -13562,7 +13598,7 @@
       </c>
       <c r="H240" s="6"/>
       <c r="J240" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K240" s="8" t="s">
         <v>336</v>
@@ -13594,7 +13630,7 @@
       </c>
       <c r="H241" s="6"/>
       <c r="J241" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K241" s="8" t="s">
         <v>336</v>
@@ -13627,7 +13663,7 @@
       <c r="H242" s="17"/>
       <c r="I242" s="17"/>
       <c r="J242" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K242" s="19" t="s">
         <v>336</v>
@@ -13667,7 +13703,7 @@
         <v>122</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>113</v>
@@ -13682,7 +13718,7 @@
         <v>46160.0</v>
       </c>
       <c r="L243" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M243" s="6"/>
       <c r="N243" s="6"/>
@@ -13711,7 +13747,7 @@
         <v>122</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>113</v>
@@ -13726,7 +13762,7 @@
         <v>46161.0</v>
       </c>
       <c r="L244" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M244" s="6"/>
       <c r="N244" s="6"/>
@@ -13755,7 +13791,7 @@
         <v>122</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>113</v>
@@ -13770,7 +13806,7 @@
         <v>46161.0</v>
       </c>
       <c r="L245" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M245" s="6"/>
       <c r="N245" s="6"/>
@@ -13843,7 +13879,7 @@
         <v>122</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H247" s="5" t="s">
         <v>156</v>
@@ -13858,7 +13894,7 @@
         <v>46161.0</v>
       </c>
       <c r="L247" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M247" s="6"/>
       <c r="N247" s="6"/>
@@ -13887,7 +13923,7 @@
         <v>122</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>156</v>
@@ -13932,7 +13968,7 @@
       <c r="H249" s="17"/>
       <c r="I249" s="17"/>
       <c r="J249" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K249" s="19" t="s">
         <v>336</v>
@@ -13972,13 +14008,13 @@
         <v>122</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I250" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J250" s="5" t="s">
         <v>170</v>
@@ -13987,7 +14023,7 @@
         <v>46163.0</v>
       </c>
       <c r="L250" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M250" s="6"/>
       <c r="N250" s="6"/>
@@ -14016,13 +14052,13 @@
         <v>122</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I251" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J251" s="5" t="s">
         <v>170</v>
@@ -14031,7 +14067,7 @@
         <v>46163.0</v>
       </c>
       <c r="L251" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M251" s="6"/>
       <c r="N251" s="6"/>
@@ -14060,13 +14096,13 @@
         <v>122</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J252" s="5" t="s">
         <v>170</v>
@@ -14075,7 +14111,7 @@
         <v>46163.0</v>
       </c>
       <c r="L252" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M252" s="6"/>
       <c r="N252" s="6"/>
@@ -14104,13 +14140,13 @@
         <v>122</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I253" s="28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J253" s="5" t="s">
         <v>170</v>
@@ -14119,7 +14155,7 @@
         <v>46163.0</v>
       </c>
       <c r="L253" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M253" s="6"/>
       <c r="N253" s="6"/>
@@ -14155,7 +14191,7 @@
         <v>122</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H254" s="5" t="s">
         <v>156</v>
@@ -14170,7 +14206,7 @@
         <v>46163.0</v>
       </c>
       <c r="L254" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M254" s="6"/>
       <c r="N254" s="6"/>
@@ -14199,7 +14235,7 @@
         <v>122</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>156</v>
@@ -14214,7 +14250,7 @@
         <v>46163.0</v>
       </c>
       <c r="L255" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M255" s="6"/>
       <c r="N255" s="6"/>
@@ -14243,7 +14279,7 @@
         <v>122</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>156</v>
@@ -14287,7 +14323,7 @@
         <v>122</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>113</v>
@@ -14326,7 +14362,7 @@
         <v>111</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>113</v>
@@ -14367,13 +14403,13 @@
         <v>122</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I259" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J259" s="5" t="s">
         <v>349</v>
@@ -14382,7 +14418,7 @@
         <v>46168.0</v>
       </c>
       <c r="L259" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M259" s="6"/>
       <c r="N259" s="6"/>
@@ -14411,13 +14447,13 @@
         <v>122</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J260" s="5" t="s">
         <v>160</v>
@@ -14426,7 +14462,7 @@
         <v>46168.0</v>
       </c>
       <c r="L260" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M260" s="6"/>
       <c r="N260" s="6"/>
@@ -14455,13 +14491,13 @@
         <v>122</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H261" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I261" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J261" s="5" t="s">
         <v>349</v>
@@ -14470,7 +14506,7 @@
         <v>46168.0</v>
       </c>
       <c r="L261" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M261" s="6"/>
       <c r="N261" s="6"/>
@@ -14499,13 +14535,13 @@
         <v>122</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H262" s="5" t="s">
         <v>113</v>
       </c>
       <c r="I262" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J262" s="5" t="s">
         <v>160</v>
@@ -14514,7 +14550,7 @@
         <v>46168.0</v>
       </c>
       <c r="L262" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M262" s="6"/>
       <c r="N262" s="6"/>
@@ -14543,13 +14579,13 @@
         <v>122</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H263" s="5" t="s">
         <v>165</v>
       </c>
       <c r="I263" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J263" s="5" t="s">
         <v>170</v>
@@ -14558,7 +14594,7 @@
         <v>46175.0</v>
       </c>
       <c r="L263" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M263" s="6"/>
       <c r="N263" s="6"/>
@@ -14583,11 +14619,11 @@
       </c>
       <c r="F264" s="6"/>
       <c r="G264" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H264" s="6"/>
       <c r="J264" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K264" s="8" t="s">
         <v>336</v>
@@ -14615,11 +14651,11 @@
       </c>
       <c r="F265" s="6"/>
       <c r="G265" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H265" s="6"/>
       <c r="J265" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K265" s="8" t="s">
         <v>336</v>
@@ -14647,11 +14683,11 @@
       </c>
       <c r="F266" s="6"/>
       <c r="G266" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H266" s="6"/>
       <c r="J266" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K266" s="8" t="s">
         <v>336</v>
@@ -14679,11 +14715,11 @@
       </c>
       <c r="F267" s="6"/>
       <c r="G267" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H267" s="6"/>
       <c r="J267" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K267" s="8" t="s">
         <v>336</v>
@@ -14711,11 +14747,11 @@
       </c>
       <c r="F268" s="6"/>
       <c r="G268" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H268" s="6"/>
       <c r="J268" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K268" s="8" t="s">
         <v>336</v>
@@ -14743,11 +14779,11 @@
       </c>
       <c r="F269" s="6"/>
       <c r="G269" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H269" s="6"/>
       <c r="J269" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K269" s="8" t="s">
         <v>336</v>
@@ -14779,7 +14815,7 @@
       </c>
       <c r="H270" s="6"/>
       <c r="J270" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K270" s="8" t="s">
         <v>415</v>
@@ -14811,7 +14847,7 @@
       </c>
       <c r="H271" s="6"/>
       <c r="J271" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K271" s="8" t="s">
         <v>415</v>
@@ -14843,7 +14879,7 @@
       </c>
       <c r="H272" s="6"/>
       <c r="J272" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K272" s="8" t="s">
         <v>415</v>
@@ -14930,7 +14966,7 @@
       </c>
       <c r="H276" s="6"/>
       <c r="J276" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K276" s="8" t="s">
         <v>415</v>
@@ -14962,7 +14998,7 @@
       </c>
       <c r="H277" s="6"/>
       <c r="J277" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K277" s="8" t="s">
         <v>415</v>
@@ -14994,7 +15030,7 @@
       </c>
       <c r="H278" s="6"/>
       <c r="J278" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K278" s="8" t="s">
         <v>415</v>
@@ -15026,7 +15062,7 @@
       </c>
       <c r="H279" s="6"/>
       <c r="J279" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K279" s="8" t="s">
         <v>415</v>
@@ -15058,7 +15094,7 @@
       </c>
       <c r="H280" s="6"/>
       <c r="J280" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K280" s="8" t="s">
         <v>415</v>
@@ -15090,7 +15126,7 @@
       </c>
       <c r="H281" s="6"/>
       <c r="J281" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K281" s="8" t="s">
         <v>415</v>
@@ -15122,7 +15158,7 @@
       </c>
       <c r="H282" s="6"/>
       <c r="J282" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K282" s="8" t="s">
         <v>415</v>
@@ -15154,7 +15190,7 @@
       </c>
       <c r="H283" s="6"/>
       <c r="J283" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K283" s="8" t="s">
         <v>415</v>
@@ -15186,7 +15222,7 @@
       </c>
       <c r="H284" s="6"/>
       <c r="J284" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K284" s="8" t="s">
         <v>415</v>
@@ -15219,7 +15255,7 @@
       <c r="H285" s="32"/>
       <c r="I285" s="32"/>
       <c r="J285" s="32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K285" s="34" t="s">
         <v>415</v>
@@ -15564,7 +15600,7 @@
       </c>
       <c r="H300" s="6"/>
       <c r="J300" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K300" s="8" t="s">
         <v>415</v>
@@ -15596,7 +15632,7 @@
       </c>
       <c r="H301" s="6"/>
       <c r="J301" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K301" s="8" t="s">
         <v>415</v>
@@ -15628,7 +15664,7 @@
       </c>
       <c r="H302" s="6"/>
       <c r="J302" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K302" s="8" t="s">
         <v>415</v>
@@ -15660,7 +15696,7 @@
       </c>
       <c r="H303" s="6"/>
       <c r="J303" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K303" s="8" t="s">
         <v>415</v>
@@ -15692,7 +15728,7 @@
       </c>
       <c r="H304" s="6"/>
       <c r="J304" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K304" s="8" t="s">
         <v>415</v>
@@ -15724,7 +15760,7 @@
       </c>
       <c r="H305" s="6"/>
       <c r="J305" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K305" s="8" t="s">
         <v>415</v>
@@ -15756,7 +15792,7 @@
       </c>
       <c r="H306" s="6"/>
       <c r="J306" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K306" s="8" t="s">
         <v>415</v>
@@ -15788,7 +15824,7 @@
       </c>
       <c r="H307" s="6"/>
       <c r="J307" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K307" s="8" t="s">
         <v>415</v>
@@ -15820,7 +15856,7 @@
       </c>
       <c r="H308" s="6"/>
       <c r="J308" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K308" s="8" t="s">
         <v>464</v>
@@ -15852,7 +15888,7 @@
       </c>
       <c r="H309" s="6"/>
       <c r="J309" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K309" s="8" t="s">
         <v>464</v>
@@ -15884,7 +15920,7 @@
       </c>
       <c r="H310" s="6"/>
       <c r="J310" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K310" s="8" t="s">
         <v>464</v>
@@ -15916,7 +15952,7 @@
       </c>
       <c r="H311" s="6"/>
       <c r="J311" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K311" s="8" t="s">
         <v>464</v>
@@ -15948,7 +15984,7 @@
       </c>
       <c r="H312" s="6"/>
       <c r="J312" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K312" s="8" t="s">
         <v>464</v>
@@ -15980,7 +16016,7 @@
       </c>
       <c r="H313" s="6"/>
       <c r="J313" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K313" s="8" t="s">
         <v>464</v>
@@ -16008,11 +16044,11 @@
       </c>
       <c r="F314" s="6"/>
       <c r="G314" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H314" s="6"/>
       <c r="J314" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K314" s="8" t="s">
         <v>464</v>
@@ -16044,7 +16080,7 @@
       </c>
       <c r="H315" s="6"/>
       <c r="J315" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K315" s="8" t="s">
         <v>464</v>
@@ -16076,7 +16112,7 @@
       </c>
       <c r="H316" s="6"/>
       <c r="J316" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K316" s="8" t="s">
         <v>464</v>
@@ -16108,7 +16144,7 @@
       </c>
       <c r="H317" s="6"/>
       <c r="J317" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K317" s="8" t="s">
         <v>464</v>
@@ -16140,7 +16176,7 @@
       </c>
       <c r="H318" s="6"/>
       <c r="J318" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K318" s="8" t="s">
         <v>464</v>
@@ -16172,7 +16208,7 @@
       </c>
       <c r="H319" s="6"/>
       <c r="J319" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K319" s="8" t="s">
         <v>464</v>
@@ -16204,7 +16240,7 @@
       </c>
       <c r="H320" s="6"/>
       <c r="J320" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K320" s="8" t="s">
         <v>464</v>
@@ -16236,7 +16272,7 @@
       </c>
       <c r="H321" s="6"/>
       <c r="J321" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K321" s="8" t="s">
         <v>464</v>
@@ -16268,7 +16304,7 @@
       </c>
       <c r="H322" s="6"/>
       <c r="J322" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K322" s="8" t="s">
         <v>464</v>
@@ -16300,7 +16336,7 @@
       </c>
       <c r="H323" s="6"/>
       <c r="J323" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K323" s="8" t="s">
         <v>464</v>
@@ -16332,7 +16368,7 @@
       </c>
       <c r="H324" s="6"/>
       <c r="J324" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K324" s="8" t="s">
         <v>464</v>
@@ -16364,7 +16400,7 @@
       </c>
       <c r="H325" s="6"/>
       <c r="J325" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K325" s="8" t="s">
         <v>464</v>
@@ -16396,7 +16432,7 @@
       </c>
       <c r="H326" s="6"/>
       <c r="J326" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K326" s="8" t="s">
         <v>464</v>
@@ -16428,7 +16464,7 @@
       </c>
       <c r="H327" s="6"/>
       <c r="J327" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K327" s="8" t="s">
         <v>464</v>
@@ -16460,7 +16496,7 @@
       </c>
       <c r="H328" s="6"/>
       <c r="J328" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K328" s="8" t="s">
         <v>464</v>
@@ -16493,7 +16529,7 @@
       <c r="H329" s="17"/>
       <c r="I329" s="17"/>
       <c r="J329" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K329" s="19" t="s">
         <v>522</v>
@@ -16843,7 +16879,7 @@
         <v>113</v>
       </c>
       <c r="I342" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J342" s="5" t="s">
         <v>349</v>
@@ -17006,7 +17042,7 @@
         <v>46183.0</v>
       </c>
       <c r="L348" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M348" s="6"/>
       <c r="N348" s="6"/>
@@ -17270,7 +17306,7 @@
         <v>46183.0</v>
       </c>
       <c r="L359" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M359" s="6"/>
       <c r="N359" s="6"/>
@@ -17314,7 +17350,7 @@
         <v>46183.0</v>
       </c>
       <c r="L360" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M360" s="6"/>
       <c r="N360" s="6"/>
@@ -17384,7 +17420,7 @@
         <v>538</v>
       </c>
       <c r="F363" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G363" s="5"/>
       <c r="H363" s="5"/>
@@ -17426,7 +17462,7 @@
         <v>113</v>
       </c>
       <c r="I364" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J364" s="5" t="s">
         <v>349</v>
@@ -17520,7 +17556,7 @@
         <v>46183.0</v>
       </c>
       <c r="L366" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M366" s="6"/>
       <c r="N366" s="6"/>
@@ -17564,7 +17600,7 @@
         <v>46183.0</v>
       </c>
       <c r="L367" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M367" s="6"/>
       <c r="N367" s="6"/>
@@ -17679,7 +17715,7 @@
         <v>113</v>
       </c>
       <c r="I370" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J370" s="5" t="s">
         <v>170</v>
@@ -17691,7 +17727,7 @@
         <v>526</v>
       </c>
       <c r="M370" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N370" s="5" t="s">
         <v>550</v>
@@ -17747,7 +17783,7 @@
         <v>526</v>
       </c>
       <c r="M371" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N371" s="5" t="s">
         <v>550</v>
@@ -17803,7 +17839,7 @@
         <v>526</v>
       </c>
       <c r="M372" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N372" s="5" t="s">
         <v>550</v>
@@ -17859,7 +17895,7 @@
         <v>526</v>
       </c>
       <c r="M373" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N373" s="5" t="s">
         <v>550</v>
@@ -17915,7 +17951,7 @@
         <v>526</v>
       </c>
       <c r="M374" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N374" s="5" t="s">
         <v>550</v>
@@ -18053,7 +18089,7 @@
       </c>
       <c r="H378" s="6"/>
       <c r="J378" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K378" s="8" t="s">
         <v>522</v>
@@ -18085,7 +18121,7 @@
       </c>
       <c r="H379" s="6"/>
       <c r="J379" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K379" s="8" t="s">
         <v>522</v>
@@ -18117,7 +18153,7 @@
       </c>
       <c r="H380" s="6"/>
       <c r="J380" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K380" s="8" t="s">
         <v>522</v>
@@ -18149,7 +18185,7 @@
       </c>
       <c r="H381" s="6"/>
       <c r="J381" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K381" s="8" t="s">
         <v>522</v>
@@ -18181,7 +18217,7 @@
       </c>
       <c r="H382" s="6"/>
       <c r="J382" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K382" s="8" t="s">
         <v>522</v>
@@ -18211,7 +18247,7 @@
       </c>
       <c r="H383" s="6"/>
       <c r="J383" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K383" s="8" t="s">
         <v>522</v>
@@ -18243,7 +18279,7 @@
       </c>
       <c r="H384" s="6"/>
       <c r="J384" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K384" s="8" t="s">
         <v>522</v>
@@ -18275,7 +18311,7 @@
       </c>
       <c r="H385" s="6"/>
       <c r="J385" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K385" s="8" t="s">
         <v>583</v>
@@ -18305,7 +18341,7 @@
       </c>
       <c r="H386" s="6"/>
       <c r="J386" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K386" s="8" t="s">
         <v>583</v>
@@ -18337,7 +18373,7 @@
       </c>
       <c r="H387" s="6"/>
       <c r="J387" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K387" s="8" t="s">
         <v>583</v>
@@ -18369,7 +18405,7 @@
       </c>
       <c r="H388" s="6"/>
       <c r="J388" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K388" s="8" t="s">
         <v>583</v>
@@ -18401,7 +18437,7 @@
       </c>
       <c r="H389" s="6"/>
       <c r="J389" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K389" s="8" t="s">
         <v>583</v>
@@ -18433,7 +18469,7 @@
       </c>
       <c r="H390" s="6"/>
       <c r="J390" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K390" s="8" t="s">
         <v>583</v>
@@ -18463,7 +18499,7 @@
       </c>
       <c r="H391" s="6"/>
       <c r="J391" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K391" s="8" t="s">
         <v>583</v>
@@ -18495,7 +18531,7 @@
       </c>
       <c r="H392" s="6"/>
       <c r="J392" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K392" s="8" t="s">
         <v>583</v>
@@ -18527,7 +18563,7 @@
       </c>
       <c r="H393" s="6"/>
       <c r="J393" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K393" s="8" t="s">
         <v>583</v>
@@ -18559,7 +18595,7 @@
       </c>
       <c r="H394" s="6"/>
       <c r="J394" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K394" s="8" t="s">
         <v>583</v>
@@ -18591,7 +18627,7 @@
       </c>
       <c r="H395" s="6"/>
       <c r="J395" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K395" s="8" t="s">
         <v>583</v>
@@ -18623,7 +18659,7 @@
       </c>
       <c r="H396" s="6"/>
       <c r="J396" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K396" s="8" t="s">
         <v>583</v>
@@ -18655,7 +18691,7 @@
       </c>
       <c r="H397" s="6"/>
       <c r="J397" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K397" s="8" t="s">
         <v>583</v>
@@ -18687,7 +18723,7 @@
       </c>
       <c r="H398" s="6"/>
       <c r="J398" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K398" s="8" t="s">
         <v>583</v>
@@ -18719,7 +18755,7 @@
       </c>
       <c r="H399" s="6"/>
       <c r="J399" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K399" s="8" t="s">
         <v>583</v>
@@ -18751,7 +18787,7 @@
       </c>
       <c r="H400" s="6"/>
       <c r="J400" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K400" s="8" t="s">
         <v>583</v>
@@ -18783,7 +18819,7 @@
       </c>
       <c r="H401" s="6"/>
       <c r="J401" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K401" s="8" t="s">
         <v>583</v>
@@ -18815,7 +18851,7 @@
       </c>
       <c r="H402" s="6"/>
       <c r="J402" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K402" s="8" t="s">
         <v>583</v>
@@ -18847,7 +18883,7 @@
       </c>
       <c r="H403" s="6"/>
       <c r="J403" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K403" s="8" t="s">
         <v>583</v>
@@ -18879,7 +18915,7 @@
       </c>
       <c r="H404" s="6"/>
       <c r="J404" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K404" s="8" t="s">
         <v>583</v>
@@ -18911,7 +18947,7 @@
       </c>
       <c r="H405" s="6"/>
       <c r="J405" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K405" s="8" t="s">
         <v>583</v>
@@ -18943,7 +18979,7 @@
       </c>
       <c r="H406" s="6"/>
       <c r="J406" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K406" s="8" t="s">
         <v>583</v>
@@ -18975,7 +19011,7 @@
       </c>
       <c r="H407" s="6"/>
       <c r="J407" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K407" s="8" t="s">
         <v>583</v>
@@ -19005,7 +19041,7 @@
       </c>
       <c r="H408" s="6"/>
       <c r="J408" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K408" s="8" t="s">
         <v>645</v>
@@ -19037,7 +19073,7 @@
       </c>
       <c r="H409" s="6"/>
       <c r="J409" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K409" s="8" t="s">
         <v>645</v>
@@ -19065,11 +19101,11 @@
       </c>
       <c r="F410" s="6"/>
       <c r="G410" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H410" s="6"/>
       <c r="J410" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K410" s="8" t="s">
         <v>645</v>
@@ -19097,11 +19133,11 @@
       </c>
       <c r="F411" s="6"/>
       <c r="G411" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H411" s="6"/>
       <c r="J411" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K411" s="8" t="s">
         <v>645</v>
@@ -19131,7 +19167,7 @@
       </c>
       <c r="H412" s="6"/>
       <c r="J412" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K412" s="8" t="s">
         <v>645</v>
@@ -19161,7 +19197,7 @@
       </c>
       <c r="H413" s="6"/>
       <c r="J413" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K413" s="8" t="s">
         <v>645</v>
@@ -19191,7 +19227,7 @@
       </c>
       <c r="H414" s="6"/>
       <c r="J414" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K414" s="8" t="s">
         <v>645</v>
@@ -19221,7 +19257,7 @@
       </c>
       <c r="H415" s="6"/>
       <c r="J415" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K415" s="8" t="s">
         <v>645</v>
@@ -19253,7 +19289,7 @@
       </c>
       <c r="H416" s="6"/>
       <c r="J416" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K416" s="8" t="s">
         <v>645</v>
@@ -19285,7 +19321,7 @@
       </c>
       <c r="H417" s="6"/>
       <c r="J417" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K417" s="8" t="s">
         <v>645</v>
@@ -19317,7 +19353,7 @@
       </c>
       <c r="H418" s="6"/>
       <c r="J418" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K418" s="8" t="s">
         <v>645</v>
@@ -19347,7 +19383,7 @@
       </c>
       <c r="H419" s="6"/>
       <c r="J419" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K419" s="8" t="s">
         <v>645</v>
@@ -19379,7 +19415,7 @@
       </c>
       <c r="H420" s="6"/>
       <c r="J420" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K420" s="8" t="s">
         <v>645</v>
@@ -19409,7 +19445,7 @@
       </c>
       <c r="H421" s="6"/>
       <c r="J421" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K421" s="8" t="s">
         <v>645</v>
@@ -19441,7 +19477,7 @@
       </c>
       <c r="H422" s="6"/>
       <c r="J422" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K422" s="8" t="s">
         <v>645</v>
@@ -19473,7 +19509,7 @@
       </c>
       <c r="H423" s="6"/>
       <c r="J423" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K423" s="8" t="s">
         <v>645</v>
@@ -19505,7 +19541,7 @@
       </c>
       <c r="H424" s="6"/>
       <c r="J424" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K424" s="8" t="s">
         <v>645</v>
@@ -19535,7 +19571,7 @@
       </c>
       <c r="H425" s="6"/>
       <c r="J425" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K425" s="8" t="s">
         <v>645</v>
@@ -19567,7 +19603,7 @@
       </c>
       <c r="H426" s="6"/>
       <c r="J426" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K426" s="8" t="s">
         <v>645</v>
@@ -19599,7 +19635,7 @@
       </c>
       <c r="H427" s="6"/>
       <c r="J427" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K427" s="8" t="s">
         <v>645</v>
@@ -19631,7 +19667,7 @@
       </c>
       <c r="H428" s="6"/>
       <c r="J428" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K428" s="8" t="s">
         <v>645</v>
@@ -19663,7 +19699,7 @@
       </c>
       <c r="H429" s="6"/>
       <c r="J429" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K429" s="8" t="s">
         <v>700</v>
@@ -19695,7 +19731,7 @@
       </c>
       <c r="H430" s="6"/>
       <c r="J430" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K430" s="8" t="s">
         <v>700</v>
@@ -19727,7 +19763,7 @@
       </c>
       <c r="H431" s="6"/>
       <c r="J431" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K431" s="8" t="s">
         <v>700</v>
@@ -19759,7 +19795,7 @@
       </c>
       <c r="H432" s="6"/>
       <c r="J432" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K432" s="8" t="s">
         <v>700</v>
@@ -19791,7 +19827,7 @@
       </c>
       <c r="H433" s="6"/>
       <c r="J433" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K433" s="8" t="s">
         <v>700</v>
@@ -19823,7 +19859,7 @@
       </c>
       <c r="H434" s="6"/>
       <c r="J434" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K434" s="8" t="s">
         <v>700</v>
@@ -19855,7 +19891,7 @@
       </c>
       <c r="H435" s="6"/>
       <c r="J435" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K435" s="8" t="s">
         <v>700</v>
@@ -19887,7 +19923,7 @@
       </c>
       <c r="H436" s="6"/>
       <c r="J436" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K436" s="8" t="s">
         <v>720</v>
@@ -19920,7 +19956,7 @@
       <c r="H437" s="17"/>
       <c r="I437" s="17"/>
       <c r="J437" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K437" s="19" t="s">
         <v>720</v>
@@ -19978,7 +20014,7 @@
         <v>726</v>
       </c>
       <c r="M438" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N438" s="5" t="s">
         <v>550</v>
@@ -20034,7 +20070,7 @@
         <v>726</v>
       </c>
       <c r="M439" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N439" s="5" t="s">
         <v>550</v>
@@ -20090,7 +20126,7 @@
         <v>726</v>
       </c>
       <c r="M440" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N440" s="5" t="s">
         <v>550</v>
@@ -20146,7 +20182,7 @@
         <v>726</v>
       </c>
       <c r="M441" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N441" s="5" t="s">
         <v>550</v>
@@ -20202,7 +20238,7 @@
         <v>726</v>
       </c>
       <c r="M442" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N442" s="5" t="s">
         <v>550</v>
@@ -20258,7 +20294,7 @@
         <v>726</v>
       </c>
       <c r="M443" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N443" s="5" t="s">
         <v>550</v>
@@ -20314,7 +20350,7 @@
         <v>726</v>
       </c>
       <c r="M444" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N444" s="5" t="s">
         <v>550</v>
@@ -20370,7 +20406,7 @@
         <v>726</v>
       </c>
       <c r="M445" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N445" s="5" t="s">
         <v>550</v>
@@ -20426,7 +20462,7 @@
         <v>726</v>
       </c>
       <c r="M446" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N446" s="5" t="s">
         <v>550</v>
@@ -20482,7 +20518,7 @@
         <v>726</v>
       </c>
       <c r="M447" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N447" s="5" t="s">
         <v>550</v>
@@ -20538,7 +20574,7 @@
         <v>726</v>
       </c>
       <c r="M448" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N448" s="5" t="s">
         <v>550</v>
@@ -20594,7 +20630,7 @@
         <v>726</v>
       </c>
       <c r="M449" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N449" s="5" t="s">
         <v>550</v>
@@ -20650,7 +20686,7 @@
         <v>726</v>
       </c>
       <c r="M450" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N450" s="5" t="s">
         <v>550</v>
@@ -20694,7 +20730,7 @@
         <v>113</v>
       </c>
       <c r="I451" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J451" s="5" t="s">
         <v>170</v>
@@ -20706,7 +20742,7 @@
         <v>726</v>
       </c>
       <c r="M451" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N451" s="5" t="s">
         <v>550</v>
@@ -20759,25 +20795,25 @@
         <v>46261.0</v>
       </c>
       <c r="L452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R452" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="453" ht="15.75" customHeight="1">
@@ -20815,25 +20851,25 @@
         <v>46261.0</v>
       </c>
       <c r="L453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R453" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="454" ht="15.75" customHeight="1">
@@ -20874,7 +20910,7 @@
         <v>726</v>
       </c>
       <c r="M454" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N454" s="5" t="s">
         <v>550</v>
@@ -20930,7 +20966,7 @@
         <v>726</v>
       </c>
       <c r="M455" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N455" s="5" t="s">
         <v>550</v>
@@ -20983,25 +21019,25 @@
         <v>46261.0</v>
       </c>
       <c r="L456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R456" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="457" ht="15.75" customHeight="1">
@@ -21042,7 +21078,7 @@
         <v>726</v>
       </c>
       <c r="M457" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N457" s="5" t="s">
         <v>550</v>
@@ -21098,7 +21134,7 @@
         <v>726</v>
       </c>
       <c r="M458" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N458" s="5" t="s">
         <v>550</v>
@@ -21154,7 +21190,7 @@
         <v>726</v>
       </c>
       <c r="M459" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N459" s="5" t="s">
         <v>550</v>
@@ -21210,7 +21246,7 @@
         <v>726</v>
       </c>
       <c r="M460" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N460" s="5" t="s">
         <v>550</v>
@@ -21266,7 +21302,7 @@
         <v>726</v>
       </c>
       <c r="M461" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N461" s="5" t="s">
         <v>550</v>
@@ -21322,7 +21358,7 @@
         <v>726</v>
       </c>
       <c r="M462" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N462" s="5" t="s">
         <v>550</v>
@@ -21378,7 +21414,7 @@
         <v>726</v>
       </c>
       <c r="M463" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N463" s="5" t="s">
         <v>550</v>
@@ -21434,7 +21470,7 @@
         <v>726</v>
       </c>
       <c r="M464" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N464" s="5" t="s">
         <v>550</v>
@@ -21490,7 +21526,7 @@
         <v>726</v>
       </c>
       <c r="M465" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N465" s="6"/>
       <c r="O465" s="6"/>
@@ -21536,7 +21572,7 @@
         <v>726</v>
       </c>
       <c r="M466" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N466" s="6"/>
       <c r="O466" s="6"/>
@@ -21582,7 +21618,7 @@
         <v>726</v>
       </c>
       <c r="M467" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N467" s="6"/>
       <c r="O467" s="6"/>
@@ -21628,22 +21664,22 @@
         <v>146</v>
       </c>
       <c r="M468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R468" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="469" ht="15.75" customHeight="1">
@@ -21684,7 +21720,7 @@
         <v>726</v>
       </c>
       <c r="M469" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N469" s="6"/>
       <c r="O469" s="6"/>
@@ -21730,7 +21766,7 @@
         <v>726</v>
       </c>
       <c r="M470" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N470" s="6"/>
       <c r="O470" s="6"/>
@@ -21776,7 +21812,7 @@
         <v>726</v>
       </c>
       <c r="M471" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N471" s="6"/>
       <c r="O471" s="6"/>
@@ -21822,7 +21858,7 @@
         <v>726</v>
       </c>
       <c r="M472" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N472" s="6"/>
       <c r="O472" s="6"/>
@@ -21868,7 +21904,7 @@
         <v>726</v>
       </c>
       <c r="M473" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N473" s="6"/>
       <c r="O473" s="6"/>
@@ -21914,7 +21950,7 @@
         <v>726</v>
       </c>
       <c r="M474" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N474" s="6"/>
       <c r="O474" s="6"/>
@@ -21960,7 +21996,7 @@
         <v>726</v>
       </c>
       <c r="M475" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N475" s="6"/>
       <c r="O475" s="6"/>
@@ -22006,7 +22042,7 @@
         <v>726</v>
       </c>
       <c r="M476" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N476" s="6"/>
       <c r="O476" s="6"/>
@@ -22052,7 +22088,7 @@
         <v>726</v>
       </c>
       <c r="M477" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N477" s="6"/>
       <c r="O477" s="6"/>
@@ -22098,7 +22134,7 @@
         <v>726</v>
       </c>
       <c r="M478" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N478" s="6"/>
       <c r="O478" s="6"/>
@@ -22144,7 +22180,7 @@
         <v>726</v>
       </c>
       <c r="M479" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N479" s="6"/>
       <c r="O479" s="6"/>
@@ -22190,7 +22226,7 @@
         <v>726</v>
       </c>
       <c r="M480" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N480" s="6"/>
       <c r="O480" s="6"/>
@@ -22236,7 +22272,7 @@
         <v>726</v>
       </c>
       <c r="M481" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N481" s="6"/>
       <c r="O481" s="6"/>
@@ -22282,7 +22318,7 @@
         <v>726</v>
       </c>
       <c r="M482" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N482" s="6"/>
       <c r="O482" s="6"/>
@@ -22328,7 +22364,7 @@
         <v>726</v>
       </c>
       <c r="M483" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N483" s="6"/>
       <c r="O483" s="6"/>
@@ -22374,7 +22410,7 @@
         <v>726</v>
       </c>
       <c r="M484" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N484" s="6"/>
       <c r="O484" s="6"/>
@@ -22420,7 +22456,7 @@
         <v>726</v>
       </c>
       <c r="M485" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N485" s="6"/>
       <c r="O485" s="6"/>
@@ -22466,7 +22502,7 @@
         <v>726</v>
       </c>
       <c r="M486" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N486" s="6"/>
       <c r="O486" s="6"/>
@@ -22512,7 +22548,7 @@
         <v>726</v>
       </c>
       <c r="M487" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N487" s="6"/>
       <c r="O487" s="6"/>
@@ -22558,7 +22594,7 @@
         <v>726</v>
       </c>
       <c r="M488" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N488" s="6"/>
       <c r="O488" s="6"/>
@@ -22604,7 +22640,7 @@
         <v>726</v>
       </c>
       <c r="M489" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N489" s="6"/>
       <c r="O489" s="6"/>
@@ -22650,7 +22686,7 @@
         <v>726</v>
       </c>
       <c r="M490" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N490" s="6"/>
       <c r="O490" s="6"/>
@@ -22696,7 +22732,7 @@
         <v>726</v>
       </c>
       <c r="M491" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N491" s="6"/>
       <c r="O491" s="6"/>
@@ -22742,7 +22778,7 @@
         <v>726</v>
       </c>
       <c r="M492" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N492" s="6"/>
       <c r="O492" s="6"/>
@@ -22788,7 +22824,7 @@
         <v>726</v>
       </c>
       <c r="M493" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N493" s="6"/>
       <c r="O493" s="6"/>
@@ -22834,22 +22870,22 @@
         <v>146</v>
       </c>
       <c r="M494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R494" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="495" ht="15.75" customHeight="1">
@@ -22890,7 +22926,7 @@
         <v>726</v>
       </c>
       <c r="M495" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N495" s="6"/>
       <c r="O495" s="6"/>
@@ -22936,7 +22972,7 @@
         <v>146</v>
       </c>
       <c r="M496" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N496" s="6"/>
       <c r="O496" s="6"/>
@@ -22982,7 +23018,7 @@
         <v>726</v>
       </c>
       <c r="M497" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N497" s="6"/>
       <c r="O497" s="6"/>
@@ -23028,7 +23064,7 @@
         <v>146</v>
       </c>
       <c r="M498" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N498" s="6"/>
       <c r="O498" s="6"/>
@@ -23074,7 +23110,7 @@
         <v>726</v>
       </c>
       <c r="M499" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N499" s="6"/>
       <c r="O499" s="6"/>
@@ -23120,7 +23156,7 @@
         <v>146</v>
       </c>
       <c r="M500" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N500" s="6"/>
       <c r="O500" s="6"/>
@@ -23166,7 +23202,7 @@
         <v>726</v>
       </c>
       <c r="M501" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N501" s="6"/>
       <c r="O501" s="6"/>
@@ -23212,7 +23248,7 @@
         <v>726</v>
       </c>
       <c r="M502" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N502" s="6"/>
       <c r="O502" s="6"/>
@@ -23258,7 +23294,7 @@
         <v>726</v>
       </c>
       <c r="M503" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N503" s="6"/>
       <c r="O503" s="6"/>
@@ -23304,7 +23340,7 @@
         <v>726</v>
       </c>
       <c r="M504" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N504" s="6"/>
       <c r="O504" s="6"/>
@@ -23350,7 +23386,7 @@
         <v>726</v>
       </c>
       <c r="M505" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N505" s="6"/>
       <c r="O505" s="6"/>
@@ -23396,7 +23432,7 @@
         <v>726</v>
       </c>
       <c r="M506" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N506" s="6"/>
       <c r="O506" s="6"/>
@@ -23442,7 +23478,7 @@
         <v>726</v>
       </c>
       <c r="M507" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N507" s="6"/>
       <c r="O507" s="6"/>
@@ -23488,7 +23524,7 @@
         <v>726</v>
       </c>
       <c r="M508" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N508" s="6"/>
       <c r="O508" s="6"/>
@@ -23534,7 +23570,7 @@
         <v>726</v>
       </c>
       <c r="M509" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N509" s="6"/>
       <c r="O509" s="6"/>
@@ -23849,7 +23885,7 @@
       <c r="H523" s="17"/>
       <c r="I523" s="17"/>
       <c r="J523" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K523" s="19" t="s">
         <v>720</v>
@@ -23907,7 +23943,7 @@
         <v>528</v>
       </c>
       <c r="M524" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N524" s="6"/>
       <c r="O524" s="6"/>
@@ -23953,7 +23989,7 @@
         <v>845</v>
       </c>
       <c r="M525" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N525" s="6"/>
       <c r="O525" s="6"/>
@@ -23999,7 +24035,7 @@
         <v>845</v>
       </c>
       <c r="M526" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N526" s="6"/>
       <c r="O526" s="6"/>
@@ -24045,7 +24081,7 @@
         <v>845</v>
       </c>
       <c r="M527" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N527" s="6"/>
       <c r="O527" s="6"/>
@@ -24091,7 +24127,7 @@
         <v>845</v>
       </c>
       <c r="M528" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N528" s="6"/>
       <c r="O528" s="6"/>
@@ -24137,7 +24173,7 @@
         <v>845</v>
       </c>
       <c r="M529" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N529" s="6"/>
       <c r="O529" s="6"/>
@@ -24183,7 +24219,7 @@
         <v>845</v>
       </c>
       <c r="M530" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N530" s="6"/>
       <c r="O530" s="6"/>
@@ -24229,7 +24265,7 @@
         <v>845</v>
       </c>
       <c r="M531" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N531" s="6"/>
       <c r="O531" s="6"/>
@@ -24275,7 +24311,7 @@
         <v>845</v>
       </c>
       <c r="M532" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N532" s="6"/>
       <c r="O532" s="6"/>
@@ -24321,7 +24357,7 @@
         <v>845</v>
       </c>
       <c r="M533" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N533" s="6"/>
       <c r="O533" s="6"/>
@@ -24367,7 +24403,7 @@
         <v>845</v>
       </c>
       <c r="M534" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N534" s="6"/>
       <c r="O534" s="6"/>
@@ -24413,7 +24449,7 @@
         <v>845</v>
       </c>
       <c r="M535" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N535" s="6"/>
       <c r="O535" s="6"/>
@@ -24459,7 +24495,7 @@
         <v>845</v>
       </c>
       <c r="M536" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N536" s="6"/>
       <c r="O536" s="6"/>
@@ -24505,7 +24541,7 @@
         <v>845</v>
       </c>
       <c r="M537" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N537" s="6"/>
       <c r="O537" s="6"/>
@@ -24551,7 +24587,7 @@
         <v>845</v>
       </c>
       <c r="M538" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N538" s="6"/>
       <c r="O538" s="6"/>
@@ -24597,7 +24633,7 @@
         <v>845</v>
       </c>
       <c r="M539" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N539" s="6"/>
       <c r="O539" s="6"/>
@@ -24643,7 +24679,7 @@
         <v>845</v>
       </c>
       <c r="M540" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N540" s="6"/>
       <c r="O540" s="6"/>
@@ -24689,7 +24725,7 @@
         <v>845</v>
       </c>
       <c r="M541" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N541" s="6"/>
       <c r="O541" s="6"/>
@@ -24735,7 +24771,7 @@
         <v>845</v>
       </c>
       <c r="M542" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N542" s="6"/>
       <c r="O542" s="6"/>
@@ -24781,7 +24817,7 @@
         <v>845</v>
       </c>
       <c r="M543" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N543" s="6"/>
       <c r="O543" s="6"/>
@@ -24827,7 +24863,7 @@
         <v>845</v>
       </c>
       <c r="M544" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N544" s="6"/>
       <c r="O544" s="6"/>
@@ -24873,7 +24909,7 @@
         <v>845</v>
       </c>
       <c r="M545" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N545" s="6"/>
       <c r="O545" s="6"/>
@@ -24919,7 +24955,7 @@
         <v>845</v>
       </c>
       <c r="M546" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N546" s="6"/>
       <c r="O546" s="6"/>
@@ -24965,7 +25001,7 @@
         <v>845</v>
       </c>
       <c r="M547" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N547" s="6"/>
       <c r="O547" s="6"/>
@@ -25011,22 +25047,22 @@
         <v>146</v>
       </c>
       <c r="M548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R548" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="549" ht="15.75" customHeight="1">
@@ -25067,22 +25103,22 @@
         <v>146</v>
       </c>
       <c r="M549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R549" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="550" ht="15.75" customHeight="1">
@@ -25123,7 +25159,7 @@
         <v>845</v>
       </c>
       <c r="M550" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N550" s="6"/>
       <c r="O550" s="6"/>
@@ -25169,7 +25205,7 @@
         <v>845</v>
       </c>
       <c r="M551" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N551" s="6"/>
       <c r="O551" s="6"/>
@@ -25215,7 +25251,7 @@
         <v>845</v>
       </c>
       <c r="M552" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N552" s="6"/>
       <c r="O552" s="6"/>
@@ -25261,7 +25297,7 @@
         <v>845</v>
       </c>
       <c r="M553" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N553" s="6"/>
       <c r="O553" s="6"/>
@@ -25307,7 +25343,7 @@
         <v>845</v>
       </c>
       <c r="M554" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N554" s="6"/>
       <c r="O554" s="6"/>
@@ -25353,7 +25389,7 @@
         <v>845</v>
       </c>
       <c r="M555" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N555" s="6"/>
       <c r="O555" s="6"/>
@@ -25399,7 +25435,7 @@
         <v>845</v>
       </c>
       <c r="M556" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N556" s="6"/>
       <c r="O556" s="6"/>
@@ -25445,7 +25481,7 @@
         <v>845</v>
       </c>
       <c r="M557" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N557" s="6"/>
       <c r="O557" s="6"/>
@@ -25491,7 +25527,7 @@
         <v>845</v>
       </c>
       <c r="M558" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N558" s="6"/>
       <c r="O558" s="6"/>
@@ -25537,7 +25573,7 @@
         <v>845</v>
       </c>
       <c r="M559" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N559" s="6"/>
       <c r="O559" s="6"/>
@@ -25583,7 +25619,7 @@
         <v>845</v>
       </c>
       <c r="M560" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N560" s="6"/>
       <c r="O560" s="6"/>
@@ -25629,7 +25665,7 @@
         <v>845</v>
       </c>
       <c r="M561" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N561" s="6"/>
       <c r="O561" s="6"/>
@@ -25675,7 +25711,7 @@
         <v>845</v>
       </c>
       <c r="M562" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N562" s="6"/>
       <c r="O562" s="6"/>
@@ -25721,7 +25757,7 @@
         <v>845</v>
       </c>
       <c r="M563" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N563" s="6"/>
       <c r="O563" s="6"/>
@@ -25767,7 +25803,7 @@
         <v>845</v>
       </c>
       <c r="M564" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N564" s="6"/>
       <c r="O564" s="6"/>
@@ -25813,7 +25849,7 @@
         <v>845</v>
       </c>
       <c r="M565" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N565" s="6"/>
       <c r="O565" s="6"/>
@@ -25859,7 +25895,7 @@
         <v>845</v>
       </c>
       <c r="M566" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N566" s="6"/>
       <c r="O566" s="6"/>
@@ -25905,7 +25941,7 @@
         <v>845</v>
       </c>
       <c r="M567" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N567" s="6"/>
       <c r="O567" s="6"/>
@@ -25951,7 +25987,7 @@
         <v>845</v>
       </c>
       <c r="M568" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N568" s="6"/>
       <c r="O568" s="6"/>
@@ -25997,7 +26033,7 @@
         <v>845</v>
       </c>
       <c r="M569" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N569" s="6"/>
       <c r="O569" s="6"/>
@@ -26043,7 +26079,7 @@
         <v>845</v>
       </c>
       <c r="M570" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N570" s="6"/>
       <c r="O570" s="6"/>
@@ -26089,7 +26125,7 @@
         <v>845</v>
       </c>
       <c r="M571" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N571" s="6"/>
       <c r="O571" s="6"/>
@@ -26135,7 +26171,7 @@
         <v>845</v>
       </c>
       <c r="M572" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N572" s="6"/>
       <c r="O572" s="6"/>
@@ -26181,7 +26217,7 @@
         <v>845</v>
       </c>
       <c r="M573" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N573" s="6"/>
       <c r="O573" s="6"/>
@@ -26227,7 +26263,7 @@
         <v>845</v>
       </c>
       <c r="M574" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N574" s="6"/>
       <c r="O574" s="6"/>
@@ -26273,7 +26309,7 @@
         <v>845</v>
       </c>
       <c r="M575" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N575" s="6"/>
       <c r="O575" s="6"/>
@@ -26319,7 +26355,7 @@
         <v>845</v>
       </c>
       <c r="M576" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N576" s="6"/>
       <c r="O576" s="6"/>
@@ -26365,7 +26401,7 @@
         <v>845</v>
       </c>
       <c r="M577" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N577" s="6"/>
       <c r="O577" s="6"/>
@@ -26411,7 +26447,7 @@
         <v>845</v>
       </c>
       <c r="M578" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N578" s="6"/>
       <c r="O578" s="6"/>
@@ -26457,7 +26493,7 @@
         <v>845</v>
       </c>
       <c r="M579" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N579" s="6"/>
       <c r="O579" s="6"/>
@@ -26503,7 +26539,7 @@
         <v>845</v>
       </c>
       <c r="M580" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N580" s="6"/>
       <c r="O580" s="6"/>
@@ -26549,7 +26585,7 @@
         <v>845</v>
       </c>
       <c r="M581" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N581" s="6"/>
       <c r="O581" s="6"/>
@@ -26595,7 +26631,7 @@
         <v>845</v>
       </c>
       <c r="M582" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N582" s="6"/>
       <c r="O582" s="6"/>
@@ -26641,7 +26677,7 @@
         <v>845</v>
       </c>
       <c r="M583" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N583" s="6"/>
       <c r="O583" s="6"/>
@@ -26687,7 +26723,7 @@
         <v>845</v>
       </c>
       <c r="M584" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N584" s="6"/>
       <c r="O584" s="6"/>
@@ -26733,7 +26769,7 @@
         <v>845</v>
       </c>
       <c r="M585" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N585" s="6"/>
       <c r="O585" s="6"/>
@@ -26779,7 +26815,7 @@
         <v>845</v>
       </c>
       <c r="M586" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N586" s="6"/>
       <c r="O586" s="6"/>
@@ -26825,7 +26861,7 @@
         <v>845</v>
       </c>
       <c r="M587" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N587" s="6"/>
       <c r="O587" s="6"/>
@@ -26871,7 +26907,7 @@
         <v>845</v>
       </c>
       <c r="M588" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N588" s="6"/>
       <c r="O588" s="6"/>
@@ -26917,7 +26953,7 @@
         <v>845</v>
       </c>
       <c r="M589" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N589" s="6"/>
       <c r="O589" s="6"/>
@@ -26963,7 +26999,7 @@
         <v>845</v>
       </c>
       <c r="M590" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N590" s="6"/>
       <c r="O590" s="6"/>
@@ -27009,7 +27045,7 @@
         <v>845</v>
       </c>
       <c r="M591" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N591" s="6"/>
       <c r="O591" s="6"/>
@@ -27055,7 +27091,7 @@
         <v>845</v>
       </c>
       <c r="M592" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N592" s="6"/>
       <c r="O592" s="6"/>
@@ -27101,7 +27137,7 @@
         <v>845</v>
       </c>
       <c r="M593" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N593" s="6"/>
       <c r="O593" s="6"/>
@@ -27147,7 +27183,7 @@
         <v>845</v>
       </c>
       <c r="M594" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N594" s="6"/>
       <c r="O594" s="6"/>
@@ -27193,7 +27229,7 @@
         <v>845</v>
       </c>
       <c r="M595" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N595" s="6"/>
       <c r="O595" s="6"/>
@@ -27239,7 +27275,7 @@
         <v>845</v>
       </c>
       <c r="M596" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N596" s="6"/>
       <c r="O596" s="6"/>
@@ -27285,7 +27321,7 @@
         <v>845</v>
       </c>
       <c r="M597" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N597" s="6"/>
       <c r="O597" s="6"/>
@@ -27331,7 +27367,7 @@
         <v>845</v>
       </c>
       <c r="M598" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N598" s="6"/>
       <c r="O598" s="6"/>
@@ -27374,25 +27410,25 @@
         <v>46189.0</v>
       </c>
       <c r="L599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R599" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="600" ht="15.75" customHeight="1">
@@ -27430,25 +27466,25 @@
         <v>46189.0</v>
       </c>
       <c r="L600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R600" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="601" ht="15.75" customHeight="1">
@@ -27489,7 +27525,7 @@
         <v>845</v>
       </c>
       <c r="M601" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N601" s="6"/>
       <c r="O601" s="6"/>
@@ -27535,7 +27571,7 @@
         <v>845</v>
       </c>
       <c r="M602" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N602" s="6"/>
       <c r="O602" s="6"/>
@@ -27581,7 +27617,7 @@
         <v>845</v>
       </c>
       <c r="M603" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N603" s="6"/>
       <c r="O603" s="6"/>
@@ -27627,7 +27663,7 @@
         <v>845</v>
       </c>
       <c r="M604" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N604" s="6"/>
       <c r="O604" s="6"/>
@@ -27673,7 +27709,7 @@
         <v>845</v>
       </c>
       <c r="M605" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N605" s="6"/>
       <c r="O605" s="6"/>
@@ -27719,7 +27755,7 @@
         <v>845</v>
       </c>
       <c r="M606" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N606" s="6"/>
       <c r="O606" s="6"/>
@@ -27765,7 +27801,7 @@
         <v>845</v>
       </c>
       <c r="M607" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N607" s="6"/>
       <c r="O607" s="6"/>
@@ -27811,7 +27847,7 @@
         <v>845</v>
       </c>
       <c r="M608" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N608" s="6"/>
       <c r="O608" s="6"/>
@@ -27857,7 +27893,7 @@
         <v>845</v>
       </c>
       <c r="M609" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N609" s="6"/>
       <c r="O609" s="6"/>
@@ -27903,7 +27939,7 @@
         <v>845</v>
       </c>
       <c r="M610" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N610" s="6"/>
       <c r="O610" s="6"/>
@@ -27949,7 +27985,7 @@
         <v>845</v>
       </c>
       <c r="M611" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N611" s="6"/>
       <c r="O611" s="6"/>
@@ -27995,7 +28031,7 @@
         <v>845</v>
       </c>
       <c r="M612" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N612" s="6"/>
       <c r="O612" s="6"/>
@@ -28041,7 +28077,7 @@
         <v>845</v>
       </c>
       <c r="M613" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N613" s="6"/>
       <c r="O613" s="6"/>
@@ -28087,7 +28123,7 @@
         <v>845</v>
       </c>
       <c r="M614" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N614" s="6"/>
       <c r="O614" s="6"/>
@@ -28133,7 +28169,7 @@
         <v>845</v>
       </c>
       <c r="M615" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N615" s="6"/>
       <c r="O615" s="6"/>
@@ -28179,7 +28215,7 @@
         <v>845</v>
       </c>
       <c r="M616" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N616" s="6"/>
       <c r="O616" s="6"/>
@@ -28225,7 +28261,7 @@
         <v>845</v>
       </c>
       <c r="M617" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N617" s="6"/>
       <c r="O617" s="6"/>
@@ -28271,7 +28307,7 @@
         <v>845</v>
       </c>
       <c r="M618" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N618" s="6"/>
       <c r="O618" s="6"/>
@@ -28317,7 +28353,7 @@
         <v>845</v>
       </c>
       <c r="M619" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N619" s="6"/>
       <c r="O619" s="6"/>
@@ -28363,7 +28399,7 @@
         <v>845</v>
       </c>
       <c r="M620" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N620" s="6"/>
       <c r="O620" s="6"/>
@@ -28409,7 +28445,7 @@
         <v>845</v>
       </c>
       <c r="M621" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N621" s="6"/>
       <c r="O621" s="6"/>
@@ -28455,7 +28491,7 @@
         <v>845</v>
       </c>
       <c r="M622" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N622" s="6"/>
       <c r="O622" s="6"/>
@@ -28501,7 +28537,7 @@
         <v>845</v>
       </c>
       <c r="M623" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N623" s="6"/>
       <c r="O623" s="6"/>
@@ -28547,7 +28583,7 @@
         <v>845</v>
       </c>
       <c r="M624" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N624" s="6"/>
       <c r="O624" s="6"/>
@@ -28593,7 +28629,7 @@
         <v>845</v>
       </c>
       <c r="M625" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N625" s="6"/>
       <c r="O625" s="6"/>
@@ -28639,7 +28675,7 @@
         <v>845</v>
       </c>
       <c r="M626" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N626" s="6"/>
       <c r="O626" s="6"/>
@@ -28685,7 +28721,7 @@
         <v>845</v>
       </c>
       <c r="M627" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N627" s="6"/>
       <c r="O627" s="6"/>
@@ -28731,7 +28767,7 @@
         <v>845</v>
       </c>
       <c r="M628" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N628" s="6"/>
       <c r="O628" s="6"/>
@@ -28777,7 +28813,7 @@
         <v>845</v>
       </c>
       <c r="M629" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N629" s="6"/>
       <c r="O629" s="6"/>
@@ -28823,7 +28859,7 @@
         <v>845</v>
       </c>
       <c r="M630" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N630" s="6"/>
       <c r="O630" s="6"/>
@@ -28869,7 +28905,7 @@
         <v>845</v>
       </c>
       <c r="M631" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N631" s="6"/>
       <c r="O631" s="6"/>
@@ -28915,7 +28951,7 @@
         <v>845</v>
       </c>
       <c r="M632" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N632" s="6"/>
       <c r="O632" s="6"/>
@@ -28961,7 +28997,7 @@
         <v>845</v>
       </c>
       <c r="M633" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N633" s="6"/>
       <c r="O633" s="6"/>
@@ -29007,7 +29043,7 @@
         <v>845</v>
       </c>
       <c r="M634" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N634" s="6"/>
       <c r="O634" s="6"/>
@@ -29053,7 +29089,7 @@
         <v>845</v>
       </c>
       <c r="M635" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N635" s="6"/>
       <c r="O635" s="6"/>
@@ -29099,7 +29135,7 @@
         <v>845</v>
       </c>
       <c r="M636" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N636" s="6"/>
       <c r="O636" s="6"/>
@@ -29145,7 +29181,7 @@
         <v>845</v>
       </c>
       <c r="M637" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N637" s="6"/>
       <c r="O637" s="6"/>
@@ -29191,7 +29227,7 @@
         <v>845</v>
       </c>
       <c r="M638" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N638" s="6"/>
       <c r="O638" s="6"/>
@@ -29237,7 +29273,7 @@
         <v>845</v>
       </c>
       <c r="M639" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N639" s="6"/>
       <c r="O639" s="6"/>
@@ -29283,7 +29319,7 @@
         <v>845</v>
       </c>
       <c r="M640" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N640" s="6"/>
       <c r="O640" s="6"/>
@@ -29329,7 +29365,7 @@
         <v>845</v>
       </c>
       <c r="M641" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N641" s="6"/>
       <c r="O641" s="6"/>
@@ -29375,7 +29411,7 @@
         <v>845</v>
       </c>
       <c r="M642" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N642" s="6"/>
       <c r="O642" s="6"/>
@@ -29421,7 +29457,7 @@
         <v>845</v>
       </c>
       <c r="M643" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N643" s="6"/>
       <c r="O643" s="6"/>
@@ -29467,7 +29503,7 @@
         <v>845</v>
       </c>
       <c r="M644" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N644" s="6"/>
       <c r="O644" s="6"/>
@@ -29513,7 +29549,7 @@
         <v>845</v>
       </c>
       <c r="M645" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N645" s="6"/>
       <c r="O645" s="6"/>
@@ -29559,7 +29595,7 @@
         <v>845</v>
       </c>
       <c r="M646" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N646" s="6"/>
       <c r="O646" s="6"/>
@@ -29605,7 +29641,7 @@
         <v>845</v>
       </c>
       <c r="M647" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N647" s="6"/>
       <c r="O647" s="6"/>
@@ -29648,25 +29684,25 @@
         <v>46189.0</v>
       </c>
       <c r="L648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R648" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="649" ht="15.75" customHeight="1">
@@ -29704,25 +29740,25 @@
         <v>46189.0</v>
       </c>
       <c r="L649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R649" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="650" ht="15.75" customHeight="1">
@@ -29763,7 +29799,7 @@
         <v>845</v>
       </c>
       <c r="M650" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N650" s="6"/>
       <c r="O650" s="6"/>
@@ -29809,7 +29845,7 @@
         <v>845</v>
       </c>
       <c r="M651" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N651" s="6"/>
       <c r="O651" s="6"/>
@@ -29855,7 +29891,7 @@
         <v>845</v>
       </c>
       <c r="M652" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N652" s="6"/>
       <c r="O652" s="6"/>
@@ -29901,7 +29937,7 @@
         <v>845</v>
       </c>
       <c r="M653" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N653" s="6"/>
       <c r="O653" s="6"/>
@@ -29947,7 +29983,7 @@
         <v>845</v>
       </c>
       <c r="M654" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N654" s="6"/>
       <c r="O654" s="6"/>
@@ -29993,7 +30029,7 @@
         <v>845</v>
       </c>
       <c r="M655" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N655" s="6"/>
       <c r="O655" s="6"/>
@@ -30039,7 +30075,7 @@
         <v>845</v>
       </c>
       <c r="M656" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N656" s="6"/>
       <c r="O656" s="6"/>
@@ -30085,7 +30121,7 @@
         <v>845</v>
       </c>
       <c r="M657" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N657" s="6"/>
       <c r="O657" s="6"/>
@@ -30131,7 +30167,7 @@
         <v>845</v>
       </c>
       <c r="M658" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N658" s="6"/>
       <c r="O658" s="6"/>
@@ -30177,7 +30213,7 @@
         <v>845</v>
       </c>
       <c r="M659" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N659" s="6"/>
       <c r="O659" s="6"/>
@@ -30223,7 +30259,7 @@
         <v>845</v>
       </c>
       <c r="M660" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N660" s="6"/>
       <c r="O660" s="6"/>
@@ -30269,7 +30305,7 @@
         <v>845</v>
       </c>
       <c r="M661" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N661" s="6"/>
       <c r="O661" s="6"/>
@@ -30315,7 +30351,7 @@
         <v>845</v>
       </c>
       <c r="M662" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N662" s="6"/>
       <c r="O662" s="6"/>
@@ -30361,7 +30397,7 @@
         <v>845</v>
       </c>
       <c r="M663" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N663" s="6"/>
       <c r="O663" s="6"/>
@@ -30407,7 +30443,7 @@
         <v>845</v>
       </c>
       <c r="M664" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N664" s="6"/>
       <c r="O664" s="6"/>
@@ -30453,7 +30489,7 @@
         <v>845</v>
       </c>
       <c r="M665" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N665" s="6"/>
       <c r="O665" s="6"/>
@@ -30499,7 +30535,7 @@
         <v>845</v>
       </c>
       <c r="M666" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N666" s="6"/>
       <c r="O666" s="6"/>
@@ -30545,7 +30581,7 @@
         <v>845</v>
       </c>
       <c r="M667" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N667" s="6"/>
       <c r="O667" s="6"/>
@@ -30591,7 +30627,7 @@
         <v>845</v>
       </c>
       <c r="M668" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N668" s="6"/>
       <c r="O668" s="6"/>
@@ -30637,7 +30673,7 @@
         <v>845</v>
       </c>
       <c r="M669" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N669" s="6"/>
       <c r="O669" s="6"/>
@@ -30708,7 +30744,7 @@
       <c r="H671" s="17"/>
       <c r="I671" s="17"/>
       <c r="J671" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K671" s="19" t="s">
         <v>720</v>
@@ -30763,25 +30799,25 @@
         <v>46189.0</v>
       </c>
       <c r="L672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R672" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="673" ht="15.75" customHeight="1">
@@ -30819,10 +30855,10 @@
         <v>46189.0</v>
       </c>
       <c r="L673" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M673" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N673" s="5"/>
       <c r="O673" s="5"/>
@@ -30868,7 +30904,7 @@
         <v>1039</v>
       </c>
       <c r="M674" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N674" s="5"/>
       <c r="O674" s="5"/>
@@ -30914,7 +30950,7 @@
         <v>1039</v>
       </c>
       <c r="M675" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N675" s="5"/>
       <c r="O675" s="5"/>
@@ -30960,7 +30996,7 @@
         <v>1039</v>
       </c>
       <c r="M676" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N676" s="5"/>
       <c r="O676" s="5"/>
@@ -31006,7 +31042,7 @@
         <v>1039</v>
       </c>
       <c r="M677" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N677" s="5"/>
       <c r="O677" s="5"/>
@@ -31052,7 +31088,7 @@
         <v>1039</v>
       </c>
       <c r="M678" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N678" s="5"/>
       <c r="O678" s="5"/>
@@ -31098,7 +31134,7 @@
         <v>1039</v>
       </c>
       <c r="M679" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N679" s="5"/>
       <c r="O679" s="5"/>
@@ -31144,7 +31180,7 @@
         <v>1039</v>
       </c>
       <c r="M680" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N680" s="5"/>
       <c r="O680" s="5"/>
@@ -31190,7 +31226,7 @@
         <v>1039</v>
       </c>
       <c r="M681" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N681" s="5"/>
       <c r="O681" s="5"/>
@@ -31236,7 +31272,7 @@
         <v>1039</v>
       </c>
       <c r="M682" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N682" s="5"/>
       <c r="O682" s="5"/>
@@ -31282,7 +31318,7 @@
         <v>1039</v>
       </c>
       <c r="M683" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N683" s="5"/>
       <c r="O683" s="5"/>
@@ -31328,7 +31364,7 @@
         <v>1039</v>
       </c>
       <c r="M684" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N684" s="5"/>
       <c r="O684" s="5"/>
@@ -31374,7 +31410,7 @@
         <v>1039</v>
       </c>
       <c r="M685" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N685" s="5"/>
       <c r="O685" s="5"/>
@@ -31420,7 +31456,7 @@
         <v>1039</v>
       </c>
       <c r="M686" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N686" s="5"/>
       <c r="O686" s="5"/>
@@ -31466,7 +31502,7 @@
         <v>1039</v>
       </c>
       <c r="M687" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N687" s="5"/>
       <c r="O687" s="5"/>
@@ -31512,7 +31548,7 @@
         <v>1039</v>
       </c>
       <c r="M688" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N688" s="5"/>
       <c r="O688" s="5"/>
@@ -31558,7 +31594,7 @@
         <v>1039</v>
       </c>
       <c r="M689" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N689" s="5"/>
       <c r="O689" s="5"/>
@@ -31604,7 +31640,7 @@
         <v>1039</v>
       </c>
       <c r="M690" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N690" s="5"/>
       <c r="O690" s="5"/>
@@ -31650,7 +31686,7 @@
         <v>1039</v>
       </c>
       <c r="M691" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N691" s="5"/>
       <c r="O691" s="5"/>
@@ -31696,7 +31732,7 @@
         <v>1039</v>
       </c>
       <c r="M692" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N692" s="5"/>
       <c r="O692" s="5"/>
@@ -31742,7 +31778,7 @@
         <v>1039</v>
       </c>
       <c r="M693" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N693" s="5"/>
       <c r="O693" s="5"/>
@@ -31788,7 +31824,7 @@
         <v>1039</v>
       </c>
       <c r="M694" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N694" s="5"/>
       <c r="O694" s="5"/>
@@ -31834,7 +31870,7 @@
         <v>1039</v>
       </c>
       <c r="M695" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N695" s="5"/>
       <c r="O695" s="5"/>
@@ -31880,7 +31916,7 @@
         <v>1039</v>
       </c>
       <c r="M696" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N696" s="5"/>
       <c r="O696" s="5"/>
@@ -31926,7 +31962,7 @@
         <v>146</v>
       </c>
       <c r="M697" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N697" s="5"/>
       <c r="O697" s="5"/>
@@ -31972,7 +32008,7 @@
         <v>146</v>
       </c>
       <c r="M698" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N698" s="5"/>
       <c r="O698" s="5"/>
@@ -32018,7 +32054,7 @@
         <v>1039</v>
       </c>
       <c r="M699" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N699" s="5"/>
       <c r="O699" s="5"/>
@@ -32064,7 +32100,7 @@
         <v>1039</v>
       </c>
       <c r="M700" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N700" s="5"/>
       <c r="O700" s="5"/>
@@ -32110,7 +32146,7 @@
         <v>1039</v>
       </c>
       <c r="M701" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N701" s="5"/>
       <c r="O701" s="5"/>
@@ -32156,7 +32192,7 @@
         <v>1039</v>
       </c>
       <c r="M702" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N702" s="5"/>
       <c r="O702" s="5"/>
@@ -32202,7 +32238,7 @@
         <v>1039</v>
       </c>
       <c r="M703" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N703" s="5"/>
       <c r="O703" s="5"/>
@@ -32248,7 +32284,7 @@
         <v>1039</v>
       </c>
       <c r="M704" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N704" s="5"/>
       <c r="O704" s="5"/>
@@ -32294,7 +32330,7 @@
         <v>1039</v>
       </c>
       <c r="M705" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N705" s="5"/>
       <c r="O705" s="5"/>
@@ -32340,7 +32376,7 @@
         <v>1039</v>
       </c>
       <c r="M706" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N706" s="5"/>
       <c r="O706" s="5"/>
@@ -32386,7 +32422,7 @@
         <v>1039</v>
       </c>
       <c r="M707" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N707" s="5"/>
       <c r="O707" s="5"/>
@@ -32432,7 +32468,7 @@
         <v>1039</v>
       </c>
       <c r="M708" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N708" s="5"/>
       <c r="O708" s="5"/>
@@ -32478,7 +32514,7 @@
         <v>1039</v>
       </c>
       <c r="M709" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N709" s="5"/>
       <c r="O709" s="5"/>
@@ -32507,7 +32543,7 @@
       <c r="H710" s="17"/>
       <c r="I710" s="17"/>
       <c r="J710" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K710" s="19" t="s">
         <v>720</v>
@@ -32562,25 +32598,25 @@
         <v>46189.0</v>
       </c>
       <c r="L711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R711" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="712" ht="15.75" customHeight="1">
@@ -32661,7 +32697,7 @@
         <v>123</v>
       </c>
       <c r="H715" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I715" s="5" t="s">
         <v>1104</v>
@@ -32676,22 +32712,22 @@
         <v>146</v>
       </c>
       <c r="M715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R715" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="716" ht="15.75" customHeight="1">
@@ -32717,7 +32753,7 @@
         <v>123</v>
       </c>
       <c r="H716" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I716" s="5" t="s">
         <v>1105</v>
@@ -32732,22 +32768,22 @@
         <v>146</v>
       </c>
       <c r="M716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R716" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="717" ht="15.75" customHeight="1">
@@ -32773,7 +32809,7 @@
         <v>123</v>
       </c>
       <c r="H717" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I717" s="5" t="s">
         <v>1104</v>
@@ -32788,22 +32824,22 @@
         <v>146</v>
       </c>
       <c r="M717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R717" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="718" ht="15.75" customHeight="1">
@@ -32869,7 +32905,7 @@
         <v>123</v>
       </c>
       <c r="H720" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J720" s="5" t="s">
         <v>160</v>
@@ -32882,19 +32918,19 @@
       </c>
       <c r="M720" s="6"/>
       <c r="N720" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O720" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P720" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q720" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R720" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="721" ht="15.75" customHeight="1">
@@ -32920,7 +32956,7 @@
         <v>123</v>
       </c>
       <c r="H721" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J721" s="5" t="s">
         <v>160</v>
@@ -32933,16 +32969,16 @@
       </c>
       <c r="M721" s="6"/>
       <c r="N721" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O721" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P721" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q721" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R721" s="5" t="s">
         <v>146</v>
@@ -32971,7 +33007,7 @@
         <v>123</v>
       </c>
       <c r="H722" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J722" s="5" t="s">
         <v>160</v>
@@ -32984,16 +33020,16 @@
       </c>
       <c r="M722" s="6"/>
       <c r="N722" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O722" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P722" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q722" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R722" s="5" t="s">
         <v>146</v>
@@ -33022,7 +33058,7 @@
         <v>123</v>
       </c>
       <c r="H723" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J723" s="5" t="s">
         <v>160</v>
@@ -33035,16 +33071,16 @@
       </c>
       <c r="M723" s="6"/>
       <c r="N723" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O723" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P723" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q723" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R723" s="5" t="s">
         <v>146</v>
@@ -33073,7 +33109,7 @@
         <v>123</v>
       </c>
       <c r="H724" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J724" s="5" t="s">
         <v>160</v>
@@ -33086,16 +33122,16 @@
       </c>
       <c r="M724" s="6"/>
       <c r="N724" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O724" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P724" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q724" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R724" s="5" t="s">
         <v>146</v>
@@ -33144,7 +33180,7 @@
         <v>193</v>
       </c>
       <c r="H726" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J726" s="5" t="s">
         <v>160</v>
@@ -33157,13 +33193,13 @@
       </c>
       <c r="M726" s="6"/>
       <c r="N726" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O726" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P726" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q726" s="5" t="s">
         <v>146</v>
@@ -33195,7 +33231,7 @@
         <v>193</v>
       </c>
       <c r="H727" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J727" s="5" t="s">
         <v>160</v>
@@ -33208,13 +33244,13 @@
       </c>
       <c r="M727" s="6"/>
       <c r="N727" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O727" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P727" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q727" s="5" t="s">
         <v>146</v>
@@ -33246,7 +33282,7 @@
         <v>193</v>
       </c>
       <c r="H728" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J728" s="5" t="s">
         <v>160</v>
@@ -33259,13 +33295,13 @@
       </c>
       <c r="M728" s="6"/>
       <c r="N728" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O728" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P728" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q728" s="5" t="s">
         <v>146</v>
@@ -33297,7 +33333,7 @@
         <v>193</v>
       </c>
       <c r="H729" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J729" s="5" t="s">
         <v>160</v>
@@ -33310,13 +33346,13 @@
       </c>
       <c r="M729" s="6"/>
       <c r="N729" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O729" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P729" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q729" s="5" t="s">
         <v>146</v>
@@ -33348,7 +33384,7 @@
         <v>193</v>
       </c>
       <c r="H730" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J730" s="5" t="s">
         <v>160</v>
@@ -33361,13 +33397,13 @@
       </c>
       <c r="M730" s="6"/>
       <c r="N730" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O730" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P730" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q730" s="5" t="s">
         <v>146</v>
@@ -33399,7 +33435,7 @@
         <v>193</v>
       </c>
       <c r="H731" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J731" s="5" t="s">
         <v>160</v>
@@ -33412,13 +33448,13 @@
       </c>
       <c r="M731" s="6"/>
       <c r="N731" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O731" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P731" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q731" s="5" t="s">
         <v>146</v>
@@ -33450,7 +33486,7 @@
         <v>193</v>
       </c>
       <c r="H732" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J732" s="5" t="s">
         <v>160</v>
@@ -33463,13 +33499,13 @@
       </c>
       <c r="M732" s="6"/>
       <c r="N732" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O732" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P732" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q732" s="5" t="s">
         <v>146</v>
@@ -33501,7 +33537,7 @@
         <v>193</v>
       </c>
       <c r="H733" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J733" s="5" t="s">
         <v>160</v>
@@ -33514,13 +33550,13 @@
       </c>
       <c r="M733" s="6"/>
       <c r="N733" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O733" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P733" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q733" s="5" t="s">
         <v>146</v>
@@ -33552,7 +33588,7 @@
         <v>193</v>
       </c>
       <c r="H734" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J734" s="5" t="s">
         <v>160</v>
@@ -33565,13 +33601,13 @@
       </c>
       <c r="M734" s="6"/>
       <c r="N734" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O734" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P734" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q734" s="5" t="s">
         <v>146</v>
@@ -33603,7 +33639,7 @@
         <v>193</v>
       </c>
       <c r="H735" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J735" s="5" t="s">
         <v>160</v>
@@ -33616,13 +33652,13 @@
       </c>
       <c r="M735" s="6"/>
       <c r="N735" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O735" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P735" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q735" s="5" t="s">
         <v>146</v>
@@ -33654,7 +33690,7 @@
         <v>193</v>
       </c>
       <c r="H736" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J736" s="5" t="s">
         <v>160</v>
@@ -33667,13 +33703,13 @@
       </c>
       <c r="M736" s="6"/>
       <c r="N736" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O736" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P736" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q736" s="5" t="s">
         <v>146</v>
@@ -34428,25 +34464,25 @@
         <v>46189.0</v>
       </c>
       <c r="L768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R768" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="769" ht="15.75" customHeight="1">
@@ -34484,25 +34520,25 @@
         <v>46189.0</v>
       </c>
       <c r="L769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R769" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="770" ht="15.75" customHeight="1">
@@ -34597,25 +34633,25 @@
         <v>46188.0</v>
       </c>
       <c r="L773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R773" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="774" ht="15.75" customHeight="1">
@@ -34653,25 +34689,25 @@
         <v>46188.0</v>
       </c>
       <c r="L774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R774" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="775" ht="15.75" customHeight="1">
@@ -34709,25 +34745,25 @@
         <v>46188.0</v>
       </c>
       <c r="L775" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R775" s="36" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="S775" s="37"/>
       <c r="T775" s="37"/>
@@ -34904,7 +34940,7 @@
       <c r="H779" s="17"/>
       <c r="I779" s="17"/>
       <c r="J779" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K779" s="19" t="s">
         <v>1177</v>
@@ -37214,7 +37250,7 @@
         <v>156</v>
       </c>
       <c r="I883" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J883" s="5" t="s">
         <v>170</v>
@@ -37223,25 +37259,25 @@
         <v>46188.0</v>
       </c>
       <c r="L883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R883" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="884" ht="15.75" customHeight="1">
@@ -37365,10 +37401,10 @@
         <v>46188.0</v>
       </c>
       <c r="L888" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M888" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N888" s="6"/>
       <c r="O888" s="6"/>
@@ -37412,7 +37448,7 @@
         <v>1183</v>
       </c>
       <c r="M889" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N889" s="6"/>
       <c r="O889" s="6"/>
@@ -37453,25 +37489,25 @@
         <v>46188.0</v>
       </c>
       <c r="L890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R890" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="891" ht="15.75" customHeight="1">
@@ -37510,7 +37546,7 @@
         <v>1183</v>
       </c>
       <c r="M891" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N891" s="6"/>
       <c r="O891" s="6"/>
@@ -37554,7 +37590,7 @@
         <v>1183</v>
       </c>
       <c r="M892" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N892" s="6"/>
       <c r="O892" s="6"/>
@@ -37598,7 +37634,7 @@
         <v>1183</v>
       </c>
       <c r="M893" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N893" s="6"/>
       <c r="O893" s="6"/>
@@ -37639,25 +37675,25 @@
         <v>46188.0</v>
       </c>
       <c r="L894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R894" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="895" ht="15.75" customHeight="1">
@@ -37696,7 +37732,7 @@
         <v>1183</v>
       </c>
       <c r="M895" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N895" s="6"/>
       <c r="O895" s="6"/>
@@ -37740,7 +37776,7 @@
         <v>1183</v>
       </c>
       <c r="M896" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N896" s="6"/>
       <c r="O896" s="6"/>
@@ -37784,7 +37820,7 @@
         <v>1183</v>
       </c>
       <c r="M897" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N897" s="6"/>
       <c r="O897" s="6"/>
@@ -37828,7 +37864,7 @@
         <v>1183</v>
       </c>
       <c r="M898" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N898" s="6"/>
       <c r="O898" s="6"/>
@@ -37872,7 +37908,7 @@
         <v>1183</v>
       </c>
       <c r="M899" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N899" s="6"/>
       <c r="O899" s="6"/>
@@ -37913,25 +37949,25 @@
         <v>46188.0</v>
       </c>
       <c r="L900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R900" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="901" ht="15.75" customHeight="1">
@@ -37970,7 +38006,7 @@
         <v>1183</v>
       </c>
       <c r="M901" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N901" s="6"/>
       <c r="O901" s="6"/>
@@ -38011,25 +38047,25 @@
         <v>46188.0</v>
       </c>
       <c r="L902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R902" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="903" ht="15.75" customHeight="1">
@@ -38068,7 +38104,7 @@
         <v>1183</v>
       </c>
       <c r="M903" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N903" s="6"/>
       <c r="O903" s="6"/>
@@ -38112,7 +38148,7 @@
         <v>1183</v>
       </c>
       <c r="M904" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N904" s="6"/>
       <c r="O904" s="6"/>
@@ -38156,7 +38192,7 @@
         <v>1183</v>
       </c>
       <c r="M905" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N905" s="6"/>
       <c r="O905" s="6"/>
@@ -38200,7 +38236,7 @@
         <v>1183</v>
       </c>
       <c r="M906" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N906" s="6"/>
       <c r="O906" s="6"/>
@@ -38244,7 +38280,7 @@
         <v>1183</v>
       </c>
       <c r="M907" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N907" s="6"/>
       <c r="O907" s="6"/>
@@ -38288,7 +38324,7 @@
         <v>1183</v>
       </c>
       <c r="M908" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N908" s="6"/>
       <c r="O908" s="6"/>
@@ -38332,7 +38368,7 @@
         <v>1183</v>
       </c>
       <c r="M909" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N909" s="6"/>
       <c r="O909" s="6"/>
@@ -38364,7 +38400,7 @@
         <v>113</v>
       </c>
       <c r="I910" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J910" s="5" t="s">
         <v>170</v>
@@ -38373,25 +38409,25 @@
         <v>46188.0</v>
       </c>
       <c r="L910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R910" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="911" ht="15.75" customHeight="1">
@@ -38628,7 +38664,7 @@
         <v>1217</v>
       </c>
       <c r="M920" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N920" s="6"/>
       <c r="O920" s="6"/>
@@ -38718,7 +38754,7 @@
         <v>1217</v>
       </c>
       <c r="M923" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N923" s="6"/>
       <c r="O923" s="6"/>
@@ -38762,7 +38798,7 @@
         <v>1217</v>
       </c>
       <c r="M924" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N924" s="6"/>
       <c r="O924" s="6"/>
@@ -38805,10 +38841,10 @@
         <v>46188.0</v>
       </c>
       <c r="L925" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M925" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N925" s="6"/>
       <c r="O925" s="6"/>
@@ -38851,25 +38887,25 @@
         <v>46188.0</v>
       </c>
       <c r="L926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R926" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="927" ht="15.75" customHeight="1">
@@ -38907,25 +38943,25 @@
         <v>46188.0</v>
       </c>
       <c r="L927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R927" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="928" ht="15.75" customHeight="1">
@@ -38963,25 +38999,25 @@
         <v>46188.0</v>
       </c>
       <c r="L928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R928" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="929" ht="15.75" customHeight="1">
@@ -39010,7 +39046,7 @@
         <v>165</v>
       </c>
       <c r="I929" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J929" s="5" t="s">
         <v>170</v>
@@ -39019,25 +39055,25 @@
         <v>46188.0</v>
       </c>
       <c r="L929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R929" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="930" ht="15.75" customHeight="1">
@@ -39222,7 +39258,7 @@
       </c>
       <c r="H937" s="6"/>
       <c r="J937" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K937" s="8" t="s">
         <v>1177</v>
@@ -39254,7 +39290,7 @@
       </c>
       <c r="H938" s="6"/>
       <c r="J938" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K938" s="8" t="s">
         <v>1177</v>
@@ -39286,7 +39322,7 @@
       </c>
       <c r="H939" s="6"/>
       <c r="J939" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K939" s="8" t="s">
         <v>1177</v>
@@ -39454,25 +39490,25 @@
         <v>46188.0</v>
       </c>
       <c r="L943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R943" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="944" ht="15.75" customHeight="1">
@@ -39548,25 +39584,25 @@
         <v>46188.0</v>
       </c>
       <c r="L945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R945" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="946" ht="15.75" customHeight="1">
@@ -39719,7 +39755,7 @@
         <v>113</v>
       </c>
       <c r="I949" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J949" s="5" t="s">
         <v>349</v>
@@ -39728,10 +39764,10 @@
         <v>46188.0</v>
       </c>
       <c r="L949" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M949" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N949" s="6"/>
       <c r="O949" s="6"/>
@@ -39998,25 +40034,25 @@
         <v>46188.0</v>
       </c>
       <c r="L955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R955" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="956" ht="15.75" customHeight="1">
@@ -40652,10 +40688,10 @@
         <v>46188.0</v>
       </c>
       <c r="L969" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M969" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N969" s="6"/>
       <c r="O969" s="6"/>
@@ -40870,25 +40906,25 @@
         <v>46188.0</v>
       </c>
       <c r="L974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R974" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="975" ht="15.75" customHeight="1">
@@ -40924,25 +40960,25 @@
         <v>46188.0</v>
       </c>
       <c r="L975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R975" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="976" ht="15.75" customHeight="1">
@@ -40979,7 +41015,7 @@
       </c>
       <c r="H977" s="6"/>
       <c r="J977" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K977" s="8" t="s">
         <v>1285</v>
@@ -41011,7 +41047,7 @@
       </c>
       <c r="H978" s="6"/>
       <c r="J978" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K978" s="8" t="s">
         <v>1285</v>
@@ -41043,7 +41079,7 @@
       </c>
       <c r="H979" s="6"/>
       <c r="J979" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K979" s="8" t="s">
         <v>1285</v>
@@ -41075,7 +41111,7 @@
       </c>
       <c r="H980" s="6"/>
       <c r="J980" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K980" s="8" t="s">
         <v>1285</v>
@@ -41107,7 +41143,7 @@
       </c>
       <c r="H981" s="6"/>
       <c r="J981" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K981" s="8" t="s">
         <v>1285</v>
@@ -41139,7 +41175,7 @@
       </c>
       <c r="H982" s="6"/>
       <c r="J982" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K982" s="8" t="s">
         <v>1285</v>
@@ -41171,7 +41207,7 @@
       </c>
       <c r="H983" s="6"/>
       <c r="J983" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K983" s="8" t="s">
         <v>1285</v>
@@ -41203,7 +41239,7 @@
       </c>
       <c r="H984" s="6"/>
       <c r="J984" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K984" s="8" t="s">
         <v>1285</v>
@@ -41235,7 +41271,7 @@
       </c>
       <c r="H985" s="6"/>
       <c r="J985" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K985" s="8" t="s">
         <v>1285</v>
@@ -41267,7 +41303,7 @@
       </c>
       <c r="H986" s="6"/>
       <c r="J986" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K986" s="8" t="s">
         <v>1285</v>
@@ -41299,7 +41335,7 @@
       </c>
       <c r="H987" s="6"/>
       <c r="J987" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K987" s="8" t="s">
         <v>1285</v>
@@ -41331,7 +41367,7 @@
       </c>
       <c r="H988" s="6"/>
       <c r="J988" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K988" s="8" t="s">
         <v>1285</v>
@@ -41363,7 +41399,7 @@
       </c>
       <c r="H989" s="6"/>
       <c r="J989" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K989" s="8" t="s">
         <v>1304</v>
@@ -41395,7 +41431,7 @@
       </c>
       <c r="H990" s="6"/>
       <c r="J990" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K990" s="8" t="s">
         <v>1304</v>
@@ -41427,7 +41463,7 @@
       </c>
       <c r="H991" s="6"/>
       <c r="J991" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K991" s="8" t="s">
         <v>1304</v>
@@ -41459,7 +41495,7 @@
       </c>
       <c r="H992" s="6"/>
       <c r="J992" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K992" s="8" t="s">
         <v>1304</v>
@@ -41491,7 +41527,7 @@
       </c>
       <c r="H993" s="6"/>
       <c r="J993" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K993" s="8" t="s">
         <v>1304</v>
@@ -41523,7 +41559,7 @@
       </c>
       <c r="H994" s="6"/>
       <c r="J994" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K994" s="8" t="s">
         <v>1304</v>
@@ -41555,7 +41591,7 @@
       </c>
       <c r="H995" s="6"/>
       <c r="J995" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K995" s="8" t="s">
         <v>1304</v>
@@ -41587,7 +41623,7 @@
       </c>
       <c r="H996" s="6"/>
       <c r="J996" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K996" s="8" t="s">
         <v>1304</v>
@@ -41619,7 +41655,7 @@
       </c>
       <c r="H997" s="6"/>
       <c r="J997" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K997" s="8" t="s">
         <v>1324</v>
@@ -41651,7 +41687,7 @@
       </c>
       <c r="H998" s="6"/>
       <c r="J998" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K998" s="8" t="s">
         <v>1324</v>
@@ -41683,7 +41719,7 @@
       </c>
       <c r="H999" s="6"/>
       <c r="J999" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K999" s="8" t="s">
         <v>1324</v>
@@ -41715,7 +41751,7 @@
       </c>
       <c r="H1000" s="6"/>
       <c r="J1000" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1000" s="8" t="s">
         <v>1334</v>
@@ -41747,7 +41783,7 @@
       </c>
       <c r="H1001" s="6"/>
       <c r="J1001" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1001" s="8" t="s">
         <v>1334</v>
@@ -41838,7 +41874,7 @@
         <v>113</v>
       </c>
       <c r="I1003" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J1003" s="5" t="s">
         <v>149</v>
@@ -41847,25 +41883,25 @@
         <v>46188.0</v>
       </c>
       <c r="L1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="M1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="N1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="O1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="P1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="Q1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="R1003" s="5" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1004" ht="15.75" customHeight="1">
@@ -41888,7 +41924,7 @@
       </c>
       <c r="H1004" s="6"/>
       <c r="J1004" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1004" s="8" t="s">
         <v>1334</v>
@@ -41920,7 +41956,7 @@
       </c>
       <c r="H1005" s="6"/>
       <c r="J1005" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1005" s="8" t="s">
         <v>1334</v>
@@ -41948,11 +41984,11 @@
       </c>
       <c r="F1006" s="6"/>
       <c r="G1006" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1006" s="6"/>
       <c r="J1006" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1006" s="8" t="s">
         <v>1334</v>
@@ -41984,7 +42020,7 @@
       </c>
       <c r="H1007" s="6"/>
       <c r="J1007" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1007" s="8" t="s">
         <v>1334</v>
@@ -42016,7 +42052,7 @@
       </c>
       <c r="H1008" s="6"/>
       <c r="J1008" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1008" s="8" t="s">
         <v>1334</v>
@@ -42046,7 +42082,7 @@
       </c>
       <c r="H1009" s="6"/>
       <c r="J1009" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1009" s="8" t="s">
         <v>1334</v>
@@ -42072,7 +42108,7 @@
       </c>
       <c r="H1010" s="6"/>
       <c r="J1010" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1010" s="8" t="s">
         <v>1334</v>
@@ -42096,7 +42132,7 @@
       </c>
       <c r="H1011" s="6"/>
       <c r="J1011" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1011" s="8" t="s">
         <v>1334</v>
@@ -42120,7 +42156,7 @@
       </c>
       <c r="H1012" s="6"/>
       <c r="J1012" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1012" s="8" t="s">
         <v>1334</v>
@@ -42146,7 +42182,7 @@
       </c>
       <c r="H1013" s="6"/>
       <c r="J1013" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1013" s="8" t="s">
         <v>1334</v>
@@ -42172,7 +42208,7 @@
       </c>
       <c r="H1014" s="6"/>
       <c r="J1014" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1014" s="8" t="s">
         <v>1372</v>
@@ -42198,7 +42234,7 @@
       </c>
       <c r="H1015" s="6"/>
       <c r="J1015" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1015" s="8" t="s">
         <v>1334</v>
@@ -42224,7 +42260,7 @@
       </c>
       <c r="H1016" s="6"/>
       <c r="J1016" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1016" s="8" t="s">
         <v>1334</v>
@@ -42250,7 +42286,7 @@
       </c>
       <c r="H1017" s="6"/>
       <c r="J1017" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1017" s="8" t="s">
         <v>1334</v>
@@ -42276,7 +42312,7 @@
       </c>
       <c r="H1018" s="6"/>
       <c r="J1018" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K1018" s="8" t="s">
         <v>1334</v>
